--- a/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,417 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8990000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8310000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8099000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7736000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7878000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7477000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6773000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5962000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6225000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5847000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5634000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5223000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5532000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5258000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5356000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7455000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8228000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8541000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8269000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7879000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8179000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8504000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8303000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7829000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8179000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7905000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7462000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6894000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7107000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7019000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7194000</v>
+      </c>
+      <c r="E9" s="3">
         <v>6592000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6502000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6285000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6307000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6042000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5568000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5013000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5136000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4862000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4768000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4504000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4828000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4624000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4925000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6614000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7136000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7382000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7236000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6956000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7193000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7305000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7184000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6834000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7169000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6787000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6469000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6082000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6113000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6114000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1796000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1718000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1597000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1451000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1571000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1435000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1205000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>949000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1089000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>985000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>866000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>719000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>704000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>634000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>431000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>841000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1092000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1159000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1033000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>923000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>986000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1199000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1119000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>995000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1010000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1118000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>993000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>812000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>994000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>905000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1099,100 +1111,104 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>187000</v>
+      </c>
+      <c r="E12" s="3">
         <v>186000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>163000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>174000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>178000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>160000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>154000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>141000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>145000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>140000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>134000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>135000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>128000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>137000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>142000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>173000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>190000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>176000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>179000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>173000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>178000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>177000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>175000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>172000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>192000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>189000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>196000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>211000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>262000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1283,38 +1299,41 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-36000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-83000</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-216000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-26000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-28000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1322,61 +1341,64 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-42000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>350000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3724000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>8523000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>209000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>12692000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-43000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>184000</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>2796000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>49000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>591000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>82000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>676000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>237000</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1467,8 +1489,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1498,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7522000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6859000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6761000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6514000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6501000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6296000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5592000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5225000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5361000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5082000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4972000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4720000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4986000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5196000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8872000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15437000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7664000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>20370000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7529000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7241000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7442000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7587000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7657000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7117000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10266000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7140000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7366000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6473000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7149000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6696000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1468000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1451000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1338000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1222000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1377000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1181000</v>
       </c>
       <c r="I18" s="3">
         <v>1181000</v>
       </c>
       <c r="J18" s="3">
+        <v>1181000</v>
+      </c>
+      <c r="K18" s="3">
         <v>737000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>864000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>765000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>662000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>503000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>546000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>62000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3516000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7982000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>564000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-11829000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>740000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>638000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>737000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>917000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>646000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>712000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2087000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>765000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>96000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>421000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-42000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>323000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1716,468 +1748,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E20" s="3">
         <v>73000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>82000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>56000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>91000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>75000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>95000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>24000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>29000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>56000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>16000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>19000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>69000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>22000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-59000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-29000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>30000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>20000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>31000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>34000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>16000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>41000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>48000</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>28000</v>
       </c>
       <c r="AA20" s="3">
         <v>28000</v>
       </c>
       <c r="AB20" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AC20" s="3">
         <v>73000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>92000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>70000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-73000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>2172000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2103000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1981000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1841000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2017000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1789000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1808000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1294000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1425000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1351000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1204000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1054000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1198000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>671000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2971000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7219000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1442000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-10909000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1709000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1575000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1672000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1845000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1570000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1614000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1153000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1794000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1174000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1480000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>901000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1352000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E22" s="3">
         <v>129000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>127000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>117000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>121000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>122000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>124000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>123000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>137000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>130000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>136000</v>
       </c>
       <c r="N22" s="3">
         <v>136000</v>
       </c>
       <c r="O22" s="3">
+        <v>136000</v>
+      </c>
+      <c r="P22" s="3">
         <v>144000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>138000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>52000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>78000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>142000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>162000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>178000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>163000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>105000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>171000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>147000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>97000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>151000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>161000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>171000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>157000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>99000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1433000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1395000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1293000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1161000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1347000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1134000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1152000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>638000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>756000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>691000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>542000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>386000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>471000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3627000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8089000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>452000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-11971000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>593000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>509000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>648000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>787000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>547000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>643000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2210000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>677000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>17000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>334000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-214000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>200000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>285000</v>
+      </c>
+      <c r="E24" s="3">
         <v>259000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>246000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>217000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>265000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>215000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>182000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>118000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>145000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>129000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>99000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>74000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>89000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>19000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-199000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-721000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>109000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-598000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>99000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>79000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>99000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>129000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>106000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>113000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>121000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>98000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>50000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-19000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2268,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1148000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1136000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1047000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>944000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1082000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>919000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>970000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>520000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>611000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>562000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>443000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>312000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>382000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-73000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3428000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7368000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>343000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-11373000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>494000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>430000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>549000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>658000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>441000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>530000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2195000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>556000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-81000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>284000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-195000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>190000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1112000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1123000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1033000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>934000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1064000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>907000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>959000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>510000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>601000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>550000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>431000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>299000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>374000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-82000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3434000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7376000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>333000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-11383000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>492000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>421000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>539000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>644000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>430000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>525000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2178000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>545000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-74000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>279000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-205000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2544,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2600,8 +2660,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>24</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>24</v>
@@ -2618,11 +2678,11 @@
       <c r="Z29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-76000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>24</v>
@@ -2630,14 +2690,17 @@
       <c r="AD29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AE29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2728,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2820,192 +2886,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-73000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-82000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-56000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-91000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-75000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-95000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-24000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-29000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-56000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-16000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-19000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-69000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>59000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>29000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-30000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-20000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-31000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-34000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-16000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-41000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-48000</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-28000</v>
       </c>
       <c r="AA32" s="3">
         <v>-28000</v>
       </c>
       <c r="AB32" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-73000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-92000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-70000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>73000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-31000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1112000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1123000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1033000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>934000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1064000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>907000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>959000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>510000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>601000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>550000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>431000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>299000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>374000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-82000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3434000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7376000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>333000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-11383000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>492000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>421000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>539000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>644000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>430000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>525000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>545000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-74000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>279000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-205000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3096,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1112000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1123000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1033000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>934000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1064000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>907000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>959000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>510000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>601000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>550000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>431000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>299000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>374000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-82000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3434000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7376000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>333000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-11383000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>492000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>421000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>539000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>644000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>430000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>525000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>545000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-74000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>279000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-205000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3319,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3353,836 +3438,864 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2900000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2488000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1930000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1501000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1655000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2180000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1893000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1600000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1757000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1569000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1439000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1268000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>844000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1219000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1462000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1375000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1137000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1183000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1466000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1230000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1433000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1493000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1461000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1865000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1799000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1690000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1903000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1902000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2929000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3441000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1089000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1247000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1264000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1003000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1239000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1429000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>923000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1049000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1382000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1373000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1243000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1642000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2162000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2618000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2127000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1969000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1030000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1109000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>882000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>925000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1344000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1361000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1588000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2300000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>3290000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3262000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>4315000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>5451000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>6328000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>7315000</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7812000</v>
+      </c>
+      <c r="E43" s="3">
         <v>8049000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7675000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7578000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7032000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6650000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6247000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5713000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5315000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5349000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5347000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5269000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5247000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5552000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5808000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7486000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7747000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8332000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8471000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8171000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7881000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8409000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8606000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8472000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8084000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>9436000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8925000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8636000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>9387000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>9565000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4387000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4305000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4360000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4286000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3999000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4143000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3968000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3719000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3272000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3296000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3267000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3303000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3354000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3542000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3601000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4148000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4130000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4341000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4389000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4224000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4010000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4108000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4120000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4174000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4046000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4308000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4338000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4288000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4225000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4572000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1530000</v>
+      </c>
+      <c r="E45" s="3">
         <v>949000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>925000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1032000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1078000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1209000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1285000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1172000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>928000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>800000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>781000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1325000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1312000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1284000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1381000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1288000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1486000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1186000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1125000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1223000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1063000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1112000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1125000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1244000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1278000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1218000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1792000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1606000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1058000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1532000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17718000</v>
+      </c>
+      <c r="E46" s="3">
         <v>17038000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16154000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15400000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15003000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15611000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14316000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13253000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12654000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12387000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12077000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12807000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12919000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14215000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14379000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>16266000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15530000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16151000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>16333000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>15773000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15731000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>16483000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>16900000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>18055000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>18497000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>19914000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>21273000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>21883000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>23927000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>26425000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1624000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1622000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1601000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1554000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1581000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1762000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1767000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1955000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2044000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2110000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2035000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2090000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2061000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1436000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1484000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1515000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1565000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1335000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1558000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1544000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1538000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1497000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1487000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1483000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1519000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1566000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1720000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1637000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7240000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6875000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6804000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6691000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6607000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6407000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6386000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6354000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6429000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6375000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6473000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6620000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6826000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7396000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7729000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8550000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>9270000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9605000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11359000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11533000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11679000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11739000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11504000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11556000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11576000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12338000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12358000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12507000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12821000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13004000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17323000</v>
+      </c>
+      <c r="E49" s="3">
         <v>16023000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>16085000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16134000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15974000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>16033000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16111000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16136000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16201000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16255000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16298000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16375000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16435000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16541000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16576000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>16597000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>23131000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>23394000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>33435000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>33556000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>33658000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>34064000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>34213000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>34337000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>34472000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>34653000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>34694000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>34788000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>34845000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>34794000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4273,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4365,100 +4481,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4052000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4255000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4182000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4076000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3970000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4280000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4247000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4269000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4183000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3911000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4025000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4144000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4193000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4478000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4499000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5666000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6816000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7505000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7906000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7915000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7901000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6263000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6052000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6047000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5923000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5183000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4971000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5277000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>4882000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>4734000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4549,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>47957000</v>
+      </c>
+      <c r="E54" s="3">
         <v>45813000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>44826000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>43855000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>43135000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>44093000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>42827000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>41967000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>41511000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>41038000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>40908000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>42036000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>42434000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>44066000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>44667000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>48594000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>56312000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>57990000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>70591000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>70321000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>70507000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>70046000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>70156000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>71478000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>71987000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>73569000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>74862000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>76175000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>77956000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>80594000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4675,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4709,560 +4838,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10904000</v>
+      </c>
+      <c r="E57" s="3">
         <v>9222000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8938000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8700000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9121000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9034000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8528000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8638000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8382000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7615000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7635000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7956000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8442000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9201000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9824000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10168000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10663000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10364000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9851000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9702000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10223000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9419000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9367000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9598000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10036000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9676000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9413000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9380000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9939000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9378000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1123000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1998000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1993000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2140000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1632000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>899000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>901000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>923000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>909000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1025000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>36000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>749000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>850000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1292000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>603000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1233000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>524000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>340000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>98000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>99000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1407000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3215000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3736000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4586000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3324000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1289000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2224000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2449000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3153000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3739000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1368000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1308000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1232000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1412000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1265000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1201000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1154000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1135000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1068000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1095000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1113000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1168000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1199000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1158000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1238000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1861000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1911000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1779000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1824000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1896000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1856000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1966000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1963000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2011000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1922000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2049000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1890000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1947000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1967000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1855000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13395000</v>
+      </c>
+      <c r="E60" s="3">
         <v>12528000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12163000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12252000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12018000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11134000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10583000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10696000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10359000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9735000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8784000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9873000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10491000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11651000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11665000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13262000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13098000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12483000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11773000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11697000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>13486000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>14600000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>15066000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>16195000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>15282000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>13014000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>13527000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>13776000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>15059000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>14972000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10842000</v>
+      </c>
+      <c r="E61" s="3">
         <v>11147000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11342000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10698000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10594000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12452000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12946000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13163000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13286000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14370000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>15687000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15834000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>16036000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>16471000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>16763000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>15409000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14770000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>16333000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>16978000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>16449000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>14644000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14159000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>13865000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>13526000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>14875000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>15871000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>16600000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>16538000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>16463000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>17538000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2361000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2431000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2387000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2525000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2534000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2996000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2673000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2469000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2580000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3268000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3378000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3357000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3418000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3575000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3783000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3940000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4268000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4847000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5567000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5651000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5791000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4339000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4328000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4431000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4569000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4674000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4783000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4807000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4905000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5510000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5353,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5445,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5537,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27768000</v>
+      </c>
+      <c r="E66" s="3">
         <v>26427000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26218000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25787000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25450000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>26894000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>26502000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26620000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26507000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27676000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>28146000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>29493000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>30363000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>32125000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>32627000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>33033000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>32552000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>34077000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>34739000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>34218000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>34345000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>33513000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>33672000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>34554000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>35145000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>33996000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>35342000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>35569000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>36878000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>38360000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5663,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5755,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5847,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5939,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6031,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>13497000</v>
+      </c>
+      <c r="E72" s="3">
         <v>12742000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11974000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11296000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10719000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9904000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9244000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8532000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8199000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7775000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7399000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7142000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7018000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6818000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7073000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>10681000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18751000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>19111000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>31186000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>31386000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>31658000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>31712000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>31760000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>32022000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>32190000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>35136000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>35284000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>36052000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>36470000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>37370000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6215,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6307,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6399,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20189000</v>
+      </c>
+      <c r="E76" s="3">
         <v>19386000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18608000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18068000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17685000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17199000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16325000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15347000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15004000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13362000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12762000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12543000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12071000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11941000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12040000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15561000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>23760000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>23913000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>35852000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>36103000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>36162000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>36533000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>36484000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>36924000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>36842000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>39573000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>39520000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>40606000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>41078000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>42234000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6583,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1112000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1123000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1033000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>934000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1064000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>907000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>959000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>510000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>601000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>550000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>431000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>299000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>374000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-82000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3434000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7376000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>333000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-11383000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>492000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>421000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>539000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>644000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>430000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>525000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>545000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-74000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>279000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-205000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6806,100 +7003,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>609000</v>
+      </c>
+      <c r="E83" s="3">
         <v>579000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>561000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>563000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>549000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>533000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>532000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>533000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>532000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>530000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>526000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>532000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>583000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>587000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>604000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>792000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>848000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>900000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>938000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>903000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>919000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>887000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>876000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>874000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>906000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>956000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>986000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>989000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1016000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>998000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6990,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7082,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7174,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7266,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7358,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3022000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1677000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1608000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>330000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1614000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1567000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>408000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>131000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1932000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1070000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1220000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>429000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>878000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>479000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>803000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>784000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2252000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1745000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1108000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>326000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2331000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1827000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>987000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>568000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2251000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1898000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>858000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>656000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2013000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1406000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7484,100 +7703,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-594000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-464000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-471000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-410000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-572000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-382000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-360000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-304000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-447000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-273000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-243000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-178000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-258000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-251000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-407000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-494000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-413000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-404000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-413000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-621000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-565000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-520000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-454000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-625000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-598000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-503000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-381000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-654000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-403000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7668,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7760,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-520000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-733000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-983000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-547000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-272000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1083000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>82000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-115000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-526000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-619000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>15000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>211000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>246000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-740000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-547000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1312000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-203000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-934000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-644000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-230000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-315000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-895000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-112000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>282000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>221000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>473000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-55000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-32000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7886,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7898,19 +8131,19 @@
         <v>-356000</v>
       </c>
       <c r="F96" s="3">
+        <v>-356000</v>
+      </c>
+      <c r="G96" s="3">
         <v>-249000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-248000</v>
       </c>
       <c r="H96" s="3">
         <v>-248000</v>
       </c>
       <c r="I96" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="J96" s="3">
         <v>-177000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-175000</v>
       </c>
       <c r="K96" s="3">
         <v>-175000</v>
@@ -7922,7 +8155,7 @@
         <v>-175000</v>
       </c>
       <c r="N96" s="3">
-        <v>-174000</v>
+        <v>-175000</v>
       </c>
       <c r="O96" s="3">
         <v>-174000</v>
@@ -7931,10 +8164,10 @@
         <v>-174000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-694000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-692000</v>
       </c>
       <c r="S96" s="3">
         <v>-692000</v>
@@ -7943,34 +8176,34 @@
         <v>-692000</v>
       </c>
       <c r="U96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-693000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-692000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-693000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-692000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-693000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-692000</v>
       </c>
       <c r="AA96" s="3">
         <v>-692000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-697000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-696000</v>
       </c>
       <c r="AE96" s="3">
         <v>-696000</v>
@@ -7978,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>-696000</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>-696000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8070,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8162,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8254,280 +8496,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2009000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-382000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-183000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>62000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1844000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-180000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-188000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-170000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1220000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-322000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1070000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-212000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1504000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>21000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-167000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>777000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2097000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1090000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-234000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-297000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2069000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-900000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1264000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-787000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>278000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2342000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1332000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1637000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2389000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1116000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-13000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-23000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-17000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>6000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>5000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-11000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>6000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-7000</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>3000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>10000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>9000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-104000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>412000</v>
+      </c>
+      <c r="E102" s="3">
         <v>558000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>429000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-154000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-525000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>287000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>293000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-157000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>188000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>130000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>171000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>424000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-375000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-243000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>87000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>238000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-46000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-283000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>236000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-203000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-60000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>32000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-404000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>66000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>109000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-213000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1027000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-512000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>494000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
@@ -656,429 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8707000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8990000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8310000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8099000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7736000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7878000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7477000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6773000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5962000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6225000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5847000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5634000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5223000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5532000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5258000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5356000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7455000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8228000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8541000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8269000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7879000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8179000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8504000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8303000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7829000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8179000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7905000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7462000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6894000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7107000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7019000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7007000</v>
+      </c>
+      <c r="E9" s="3">
         <v>7194000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6592000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6502000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6285000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6307000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6042000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5568000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5013000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5136000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4862000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4768000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4504000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4828000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4624000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4925000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6614000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7136000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7382000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7236000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>6956000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7193000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7305000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7184000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6834000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>7169000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6787000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6469000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6082000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6113000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>6114000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1700000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1796000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1718000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1597000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1451000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1571000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1435000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1205000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>949000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1089000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>985000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>866000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>719000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>704000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>634000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>431000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>841000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1092000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1159000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1033000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>923000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>986000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1199000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1119000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>995000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1010000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1118000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>993000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>812000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>994000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>905000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,103 +1125,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E12" s="3">
         <v>187000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>186000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>163000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>174000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>178000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>160000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>154000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>141000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>145000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>140000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>134000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>135000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>128000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>137000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>142000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>173000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>190000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>176000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>179000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>173000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>178000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>177000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>175000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>172000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>192000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>189000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>196000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>211000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>262000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1302,41 +1319,44 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E14" s="3">
         <v>45000</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-36000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-83000</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-216000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-26000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-28000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1344,61 +1364,64 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-42000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>350000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3724000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>8523000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>209000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>12692000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-43000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>184000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>2796000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>49000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>591000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>82000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>676000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>237000</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1550,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7321000</v>
+      </c>
+      <c r="E17" s="3">
         <v>7522000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6859000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6761000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6514000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6501000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6296000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5592000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5225000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5361000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5082000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4972000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4720000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4986000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5196000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8872000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15437000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7664000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>20370000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7529000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7241000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7442000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7587000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7657000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7117000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>10266000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7140000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7366000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6473000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7149000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6696000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1386000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1468000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1451000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1338000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1222000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1377000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1181000</v>
       </c>
       <c r="J18" s="3">
         <v>1181000</v>
       </c>
       <c r="K18" s="3">
+        <v>1181000</v>
+      </c>
+      <c r="L18" s="3">
         <v>737000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>864000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>765000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>662000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>503000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>546000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>62000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3516000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7982000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>564000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-11829000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>740000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>638000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>737000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>917000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>646000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>712000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2087000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>765000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>96000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>421000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-42000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>323000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1749,483 +1782,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E20" s="3">
         <v>95000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>73000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>82000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>56000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>91000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>75000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>95000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>24000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>29000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>56000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>16000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>19000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>69000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>22000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-59000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-29000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>30000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>20000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>31000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>34000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>16000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>41000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>48000</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>28000</v>
       </c>
       <c r="AB20" s="3">
         <v>28000</v>
       </c>
       <c r="AC20" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AD20" s="3">
         <v>73000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>92000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>70000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-73000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>2070000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2172000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2103000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1981000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1841000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2017000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1789000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1808000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1294000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1425000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1351000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1204000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1054000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1198000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>671000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2971000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7219000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1442000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-10909000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1709000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1575000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1672000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1845000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1570000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1614000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1153000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1794000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1174000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1480000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>901000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1352000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E22" s="3">
         <v>130000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>129000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>127000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>117000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>121000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>122000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>124000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>123000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>137000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>130000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>136000</v>
       </c>
       <c r="O22" s="3">
         <v>136000</v>
       </c>
       <c r="P22" s="3">
+        <v>136000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>144000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>138000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>52000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>78000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>142000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>162000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>178000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>163000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>105000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>171000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>147000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>97000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>151000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>161000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>171000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>157000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>99000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1357000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1433000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1395000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1293000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1161000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1347000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1134000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1152000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>638000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>756000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>691000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>542000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>386000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>471000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-54000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3627000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8089000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>452000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11971000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>593000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>509000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>648000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>787000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>547000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>643000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2210000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>677000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>17000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>334000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-214000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>200000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E24" s="3">
         <v>285000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>259000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>246000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>217000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>265000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>215000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>182000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>118000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>145000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>129000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>99000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>74000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>89000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>19000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-199000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-721000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>109000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-598000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>99000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>79000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>99000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>129000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>106000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>113000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>121000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>98000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>50000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-19000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1098000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1148000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1136000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1047000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>944000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1082000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>919000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>970000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>520000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>611000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>562000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>443000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>312000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>382000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-73000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3428000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7368000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>343000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-11373000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>494000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>430000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>549000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>658000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>441000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>530000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2195000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>556000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-81000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>284000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-195000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>190000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1068000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1112000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1123000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1033000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>934000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1064000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>907000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>959000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>510000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>601000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>550000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>431000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>299000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>374000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-82000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3434000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7376000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>333000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-11383000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>492000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>421000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>539000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>644000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>430000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>525000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2178000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>545000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-74000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>279000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-205000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2663,8 +2724,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>24</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>24</v>
@@ -2681,11 +2742,11 @@
       <c r="AA29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-76000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>24</v>
@@ -2693,14 +2754,17 @@
       <c r="AE29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3" t="s">
+      <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +2956,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-95000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-73000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-82000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-56000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-91000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-75000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-95000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-24000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-29000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-56000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-16000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-19000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-69000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-22000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>59000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>29000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-30000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-20000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-31000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-34000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-41000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-48000</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-28000</v>
       </c>
       <c r="AB32" s="3">
         <v>-28000</v>
       </c>
       <c r="AC32" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-73000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-92000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-70000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>73000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-31000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1068000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1112000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1123000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1033000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>934000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1064000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>907000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>959000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>510000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>601000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>550000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>431000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>299000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>374000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-82000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3434000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7376000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>333000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-11383000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>492000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>421000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>539000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>644000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>430000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>525000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>545000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-74000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>279000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-205000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1068000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1112000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1123000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1033000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>934000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1064000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>907000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>959000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>510000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>601000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>550000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>431000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>299000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>374000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-82000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3434000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7376000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>333000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-11383000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>492000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>421000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>539000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>644000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>430000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>525000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>545000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-74000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>279000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-205000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,863 +3525,891 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2788000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2900000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2488000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1930000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1501000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1655000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2180000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1893000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1600000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1757000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1569000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1439000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1268000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>844000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1219000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1462000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1375000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1137000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1183000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1466000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1230000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1433000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1493000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1461000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1865000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1799000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1690000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1903000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1902000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2929000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3441000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>703000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1089000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1247000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1264000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1003000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1239000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1429000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>923000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1049000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1382000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1373000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1243000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1642000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2162000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2618000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2127000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1969000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1030000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1109000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>882000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>925000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1344000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1361000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1588000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2300000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3290000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>3262000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>4315000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>5451000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>6328000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>7315000</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8222000</v>
+      </c>
+      <c r="E43" s="3">
         <v>7812000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8049000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7675000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7578000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7032000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6650000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6247000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5713000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5315000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5349000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5347000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5269000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5247000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5552000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5808000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7486000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7747000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8332000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8471000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>8171000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7881000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8409000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8606000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8472000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8084000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>9436000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8925000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>8636000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>9387000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>9565000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4549000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4387000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4305000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4360000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4286000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3999000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4143000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3968000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3719000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3272000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3296000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3267000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3303000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3354000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3542000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3601000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4148000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4130000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4341000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4389000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4224000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4010000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4108000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4120000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4174000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4046000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4308000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4338000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4288000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4225000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4572000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1438000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1530000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>949000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>925000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1032000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1078000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1209000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1285000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1172000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>928000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>800000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>781000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1325000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1312000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1284000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1381000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1288000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1486000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1186000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1125000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1223000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1063000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1112000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1125000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1244000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1278000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1218000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1792000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1606000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1058000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1532000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17700000</v>
+      </c>
+      <c r="E46" s="3">
         <v>17718000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17038000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16154000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15400000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15003000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15611000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14316000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13253000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12654000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12387000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12077000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12807000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12919000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14215000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14379000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>16266000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15530000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>16151000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>16333000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15773000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15731000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>16483000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16900000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>18055000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>18497000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>19914000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>21273000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>21883000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>23927000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>26425000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1606000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1624000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1622000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1601000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1554000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1581000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1762000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1767000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1955000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2044000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2110000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2035000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2090000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2061000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1436000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1484000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1515000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1565000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1335000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1558000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1544000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1538000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1497000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1487000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1483000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1519000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1566000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1720000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1637000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7253000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7240000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6875000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6804000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6691000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6607000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6407000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6386000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6354000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6429000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6375000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6473000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6620000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6826000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7396000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7729000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8550000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9270000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9605000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11359000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11533000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11679000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11739000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11504000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11556000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11576000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12338000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12358000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12507000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12821000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13004000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17253000</v>
+      </c>
+      <c r="E49" s="3">
         <v>17323000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>16023000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16085000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>16134000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15974000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16033000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16111000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16136000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16201000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16255000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16298000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16375000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16435000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16541000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>16576000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>16597000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>23131000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>23394000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>33435000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>33556000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>33658000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>34064000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>34213000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>34337000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>34472000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>34653000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>34694000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>34788000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>34845000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>34794000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4601,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4044000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4052000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4255000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4182000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4076000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3970000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4280000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4247000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4269000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4183000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3911000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4025000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4144000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4193000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4478000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4499000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5666000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6816000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7505000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7906000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7915000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7901000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6263000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6052000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6047000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5923000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5183000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4971000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5277000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>4882000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4734000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4797,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>47856000</v>
+      </c>
+      <c r="E54" s="3">
         <v>47957000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>45813000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>44826000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>43855000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>43135000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44093000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42827000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>41967000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>41511000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>41038000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>40908000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>42036000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>42434000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>44066000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>44667000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>48594000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>56312000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>57990000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>70591000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>70321000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>70507000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>70046000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>70156000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>71478000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>71987000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>73569000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>74862000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>76175000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>77956000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>80594000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,578 +4969,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10051000</v>
+      </c>
+      <c r="E57" s="3">
         <v>10904000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9222000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8938000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8700000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9121000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9034000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8528000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8638000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8382000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7615000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7635000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7956000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8442000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9201000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9824000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10168000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10663000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10364000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9851000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9702000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10223000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9419000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9367000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9598000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10036000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9676000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9413000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9380000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9939000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9378000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1430000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1123000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1998000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1993000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2140000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1632000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>899000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>901000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>923000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>909000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1025000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>36000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>749000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>850000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1292000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>603000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1233000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>524000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>340000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>98000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>99000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1407000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3215000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3736000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4586000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3324000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1289000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2224000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2449000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3153000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3739000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1398000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1368000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1308000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1232000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1412000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1265000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1201000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1154000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1135000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1068000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1095000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1113000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1168000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1199000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1158000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1238000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1861000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1911000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1779000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1824000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1896000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1856000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1966000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1963000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2011000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1922000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2049000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1890000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1947000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1967000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1855000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12879000</v>
+      </c>
+      <c r="E60" s="3">
         <v>13395000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12528000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12163000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12252000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12018000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11134000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10583000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10696000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10359000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9735000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8784000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9873000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10491000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11651000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11665000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13262000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13098000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12483000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11773000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11697000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>13486000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14600000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>15066000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>16195000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>15282000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>13014000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>13527000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>13776000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>15059000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>14972000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10740000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10842000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11147000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11342000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10698000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10594000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12452000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12946000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13163000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13286000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>14370000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15687000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>15834000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>16036000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>16471000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>16763000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>15409000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14770000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>16333000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>16978000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>16449000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14644000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14159000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>13865000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>13526000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>14875000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>15871000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>16600000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>16538000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>16463000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>17538000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2314000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2361000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2431000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2387000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2525000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2534000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2996000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2673000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2469000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2580000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3268000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3378000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3357000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3418000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3575000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3783000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3940000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4268000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4847000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5567000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5651000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5791000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4339000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4328000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4431000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4569000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4674000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4783000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4807000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4905000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5510000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5849,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27120000</v>
+      </c>
+      <c r="E66" s="3">
         <v>27768000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26427000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26218000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25787000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25450000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>26894000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26502000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26620000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>26507000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>27676000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>28146000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29493000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>30363000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>32125000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>32627000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>33033000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>32552000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>34077000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>34739000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>34218000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>34345000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>33513000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>33672000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>34554000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>35145000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>33996000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>35342000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>35569000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>36878000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>38360000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6375,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14172000</v>
+      </c>
+      <c r="E72" s="3">
         <v>13497000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>12742000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11974000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11296000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10719000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9904000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9244000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8532000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8199000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7775000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7399000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7142000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7018000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6818000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7073000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>10681000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>18751000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>19111000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>31186000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>31386000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>31658000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>31712000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>31760000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>32022000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>32190000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>35136000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>35284000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>36052000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>36470000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>37370000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6767,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20736000</v>
+      </c>
+      <c r="E76" s="3">
         <v>20189000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19386000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18608000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18068000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17685000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17199000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16325000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15347000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15004000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13362000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12762000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12543000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12071000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11941000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12040000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15561000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>23760000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>23913000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>35852000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>36103000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>36162000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>36533000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>36484000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>36924000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>36842000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>39573000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>39520000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>40606000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>41078000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>42234000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1068000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1112000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1123000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1033000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>934000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1064000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>907000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>959000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>510000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>601000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>550000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>431000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>299000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>374000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-82000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3434000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7376000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>333000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-11383000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>492000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>421000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>539000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>644000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>430000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>525000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>545000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-74000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>279000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-205000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,103 +7202,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600000</v>
+      </c>
+      <c r="E83" s="3">
         <v>609000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>579000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>561000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>563000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>549000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>533000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>532000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>533000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>532000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>530000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>526000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>532000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>583000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>587000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>604000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>792000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>848000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>900000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>938000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>903000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>919000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>887000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>876000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>874000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>906000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>956000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>986000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>989000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1016000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>998000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7788,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>327000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3022000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1677000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1608000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>330000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1614000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1567000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>408000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>131000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1932000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1070000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1220000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>429000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>878000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>479000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>803000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>784000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2252000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1745000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1108000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>326000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2331000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1827000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>987000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>568000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2251000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1898000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>858000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>656000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2013000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1406000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,103 +7924,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-399000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-594000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-464000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-471000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-410000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-572000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-382000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-360000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-304000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-447000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-273000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-243000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-178000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-258000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-251000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-407000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-494000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-413000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-404000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-413000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-621000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-565000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-520000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-454000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-625000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-598000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-503000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-381000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-654000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-403000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8216,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-151000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-520000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-733000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-983000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-547000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-272000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1083000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>82000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-115000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-526000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-619000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>15000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>211000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>246000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-740000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-547000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1312000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-203000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-934000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-644000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-230000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-315000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-895000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-112000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>282000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>221000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>473000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-55000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-32000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,13 +8352,14 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-356000</v>
+        <v>-357000</v>
       </c>
       <c r="E96" s="3">
         <v>-356000</v>
@@ -8134,19 +8368,19 @@
         <v>-356000</v>
       </c>
       <c r="G96" s="3">
+        <v>-356000</v>
+      </c>
+      <c r="H96" s="3">
         <v>-249000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-248000</v>
       </c>
       <c r="I96" s="3">
         <v>-248000</v>
       </c>
       <c r="J96" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-177000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-175000</v>
       </c>
       <c r="L96" s="3">
         <v>-175000</v>
@@ -8158,7 +8392,7 @@
         <v>-175000</v>
       </c>
       <c r="O96" s="3">
-        <v>-174000</v>
+        <v>-175000</v>
       </c>
       <c r="P96" s="3">
         <v>-174000</v>
@@ -8167,10 +8401,10 @@
         <v>-174000</v>
       </c>
       <c r="R96" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-694000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-692000</v>
       </c>
       <c r="T96" s="3">
         <v>-692000</v>
@@ -8179,34 +8413,34 @@
         <v>-692000</v>
       </c>
       <c r="V96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-693000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-692000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-693000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-692000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-693000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-692000</v>
       </c>
       <c r="AB96" s="3">
         <v>-692000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-697000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-696000</v>
       </c>
       <c r="AF96" s="3">
         <v>-696000</v>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>-696000</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>-696000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,289 +8742,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-267000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2009000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-382000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-183000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>62000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1844000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-180000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-188000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-170000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1220000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-322000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1070000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-212000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1504000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>21000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-167000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>777000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2097000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1090000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-234000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-297000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2069000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-900000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1264000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-787000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>278000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2342000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1332000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1637000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2389000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1116000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-81000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-13000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-23000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-17000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>6000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>5000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-11000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-4000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>6000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>3000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>10000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>2000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>9000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-104000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-112000</v>
+      </c>
+      <c r="E102" s="3">
         <v>412000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>558000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>429000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-154000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-525000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>287000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>293000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-157000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>188000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>130000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>171000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>424000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-375000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-243000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>87000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>238000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-46000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-283000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>236000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-203000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-60000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>32000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-404000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>66000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>109000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-213000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1027000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-512000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>494000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
@@ -656,442 +656,455 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9139000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8707000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8990000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8310000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8099000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7736000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7878000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7477000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6773000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5962000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6225000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5847000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5634000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5223000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5532000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5258000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5356000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7455000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8228000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8541000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8269000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7879000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8179000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8504000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8303000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7829000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8179000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7905000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7462000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6894000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7107000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7019000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>7007000</v>
+        <v>7247000</v>
       </c>
       <c r="E9" s="3">
-        <v>7194000</v>
+        <v>6993000</v>
       </c>
       <c r="F9" s="3">
+        <v>7183000</v>
+      </c>
+      <c r="G9" s="3">
         <v>6592000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6502000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6285000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6307000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6042000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5568000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5013000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5136000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4862000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4768000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4504000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4828000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4624000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4925000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6614000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7136000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7382000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7236000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6956000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7193000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7305000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7184000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6834000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>7169000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6787000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6469000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6082000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>6113000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>6114000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1700000</v>
+        <v>1892000</v>
       </c>
       <c r="E10" s="3">
-        <v>1796000</v>
+        <v>1714000</v>
       </c>
       <c r="F10" s="3">
+        <v>1807000</v>
+      </c>
+      <c r="G10" s="3">
         <v>1718000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1597000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1451000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1571000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1435000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1205000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>949000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1089000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>985000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>866000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>719000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>704000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>634000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>431000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>841000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1092000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1159000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1033000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>923000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>986000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1199000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1119000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>995000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1010000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1118000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>993000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>812000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>994000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>905000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1126,106 +1139,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>188000</v>
+      </c>
+      <c r="E12" s="3">
         <v>182000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>187000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>186000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>163000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>174000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>178000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>160000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>154000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>141000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>145000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>140000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>134000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>135000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>128000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>137000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>142000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>173000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>190000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>176000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>179000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>173000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>178000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>177000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>175000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>172000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>192000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>189000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>196000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>211000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>262000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1322,44 +1339,47 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>11000</v>
+        <v>142000</v>
       </c>
       <c r="E14" s="3">
-        <v>45000</v>
+        <v>25000</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-36000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-83000</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-216000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-26000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-28000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1367,61 +1387,64 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-42000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>350000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3724000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>8523000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>209000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>12692000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-43000</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>184000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>2796000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>49000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>591000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>82000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>676000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>237000</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1518,8 +1541,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,204 +1577,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7671000</v>
+      </c>
+      <c r="E17" s="3">
         <v>7321000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7522000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6859000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6761000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6514000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6501000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6296000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5592000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5225000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5361000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5082000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4972000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4720000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4986000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5196000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8872000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15437000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7664000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>20370000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7529000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7241000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7442000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7587000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7657000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7117000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10266000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7140000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7366000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6473000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7149000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6696000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1468000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1386000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1468000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1451000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1338000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1222000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1377000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>1181000</v>
       </c>
       <c r="K18" s="3">
         <v>1181000</v>
       </c>
       <c r="L18" s="3">
+        <v>1181000</v>
+      </c>
+      <c r="M18" s="3">
         <v>737000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>864000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>765000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>662000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>503000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>546000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>62000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3516000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-7982000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>564000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-11829000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>740000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>638000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>737000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>917000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>646000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>712000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2087000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>765000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>96000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>421000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-42000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>323000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1783,498 +1816,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E20" s="3">
         <v>84000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>95000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>73000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>82000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>56000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>91000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>75000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>95000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>24000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>29000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>56000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>16000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>19000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>69000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>22000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-59000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-29000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>30000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>20000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>31000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>34000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>16000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>41000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>48000</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>28000</v>
       </c>
       <c r="AC20" s="3">
         <v>28000</v>
       </c>
       <c r="AD20" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AE20" s="3">
         <v>73000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>92000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>70000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-73000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>2184000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2070000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2172000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2103000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1981000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1841000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2017000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1789000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1808000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1294000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1425000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1351000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1204000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1054000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1198000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>671000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2971000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-7219000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1442000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-10909000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1709000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1575000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1672000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1845000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1570000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1614000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1153000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1794000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1174000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1480000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>901000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1352000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E22" s="3">
         <v>113000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>130000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>129000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>127000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>117000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>121000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>122000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>124000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>123000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>137000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>130000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>136000</v>
       </c>
       <c r="P22" s="3">
         <v>136000</v>
       </c>
       <c r="Q22" s="3">
+        <v>136000</v>
+      </c>
+      <c r="R22" s="3">
         <v>144000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>138000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>52000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>78000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>142000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>162000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>178000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>163000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>105000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>171000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>147000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>97000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>151000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>161000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>171000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>157000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>99000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1421000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1357000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1433000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1395000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1293000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1161000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1347000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1134000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1152000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>638000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>756000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>691000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>542000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>386000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>471000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-54000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3627000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8089000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>452000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11971000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>593000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>509000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>648000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>787000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>547000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>643000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2210000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>677000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>17000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>334000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-214000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>200000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>276000</v>
+      </c>
+      <c r="E24" s="3">
         <v>259000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>285000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>259000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>246000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>217000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>265000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>215000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>182000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>118000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>145000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>129000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>99000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>74000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>89000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>19000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-199000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-721000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>109000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-598000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>99000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>79000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>99000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>129000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>106000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>113000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>121000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>98000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>50000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-19000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2371,204 +2420,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1145000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1098000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1148000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1136000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1047000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>944000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1082000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>919000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>970000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>520000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>611000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>562000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>443000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>312000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>382000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-73000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3428000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7368000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>343000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-11373000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>494000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>430000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>549000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>658000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>441000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>530000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2195000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>556000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-81000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>284000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-195000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>190000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1112000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1068000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1112000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1123000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1033000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>934000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1064000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>907000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>959000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>510000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>601000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>550000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>431000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>299000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>374000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-82000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3434000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7376000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>333000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-11383000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>492000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>421000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>539000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>644000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>430000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>525000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2178000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>545000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-74000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>279000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-205000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2665,8 +2723,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2727,8 +2788,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>24</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>24</v>
@@ -2745,11 +2806,11 @@
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-76000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -2757,14 +2818,17 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3" t="s">
+      <c r="AG29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2925,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,204 +3026,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-84000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-95000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-73000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-82000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-56000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-91000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-75000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-95000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-24000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-29000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-56000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-16000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-69000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-22000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>59000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>29000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-30000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-20000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-31000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-34000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-16000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-48000</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-28000</v>
       </c>
       <c r="AC32" s="3">
         <v>-28000</v>
       </c>
       <c r="AD32" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-73000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-92000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-70000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>73000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-31000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1112000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1068000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1112000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1123000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1033000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>934000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1064000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>907000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>959000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>510000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>601000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>550000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>431000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>299000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>374000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-82000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3434000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7376000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>333000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-11383000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>492000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>421000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>539000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>644000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>430000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>525000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>545000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-74000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>279000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-205000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3329,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1112000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1068000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1112000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1123000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1033000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>934000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1064000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>907000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>959000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>510000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>601000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>550000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>431000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>299000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>374000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-82000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3434000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7376000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>333000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-11383000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>492000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>421000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>539000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>644000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>430000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>525000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>545000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-74000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>279000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-205000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3575,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,890 +3612,918 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2953000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2788000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2900000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2488000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1930000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1501000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1655000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2180000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1893000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1600000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1757000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1569000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1439000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1268000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>844000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1219000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1462000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1375000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1137000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1183000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1466000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1230000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1433000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1493000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1461000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1865000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1799000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1690000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1903000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1902000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2929000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3441000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1050000</v>
+      </c>
+      <c r="E42" s="3">
         <v>703000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1089000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1247000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1264000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1003000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1239000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1429000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>923000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1049000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1382000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1373000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1243000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1642000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2162000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2618000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2127000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1969000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1030000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1109000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>882000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>925000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1344000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1361000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1588000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2300000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>3290000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>3262000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>4315000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>5451000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>6328000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>7315000</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8605000</v>
+      </c>
+      <c r="E43" s="3">
         <v>8222000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7812000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8049000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7675000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7578000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7032000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6650000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6247000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5713000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5315000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5349000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5347000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5269000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5247000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5552000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5808000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7486000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7747000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8332000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>8471000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8171000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7881000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8409000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8606000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8472000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8084000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>9436000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>8925000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>8636000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>9387000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>9565000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4504000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4549000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4387000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4305000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4360000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4286000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3999000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4143000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3968000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3719000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3272000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3296000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3267000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3303000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3354000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3542000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3601000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4148000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4130000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4341000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4389000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4224000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4010000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4108000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4120000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4174000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4046000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4308000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4338000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4288000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4225000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4572000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1405000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1438000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1530000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>949000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>925000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1032000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1078000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1209000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1285000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1172000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>928000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>800000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>781000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1325000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1312000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1284000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1381000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1288000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1486000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1186000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1125000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1223000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1063000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1112000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1125000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1244000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1278000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1218000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1792000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1606000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1058000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1532000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18517000</v>
+      </c>
+      <c r="E46" s="3">
         <v>17700000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17718000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17038000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16154000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15400000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15003000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15611000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14316000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13253000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12654000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12387000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12077000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12807000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12919000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14215000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>14379000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16266000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15530000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>16151000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>16333000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15773000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>15731000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16483000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16900000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>18055000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>18497000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>19914000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>21273000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>21883000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>23927000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>26425000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1678000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1606000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1624000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1622000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1601000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1554000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1581000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1762000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1767000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1955000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2044000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2110000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2035000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2090000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2061000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1436000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1484000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1515000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1565000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1335000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1558000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1544000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1538000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1497000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1487000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1483000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1519000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1566000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1720000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1637000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7335000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7253000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7240000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6875000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6804000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6691000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6607000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6407000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6386000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6354000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6429000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6375000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6473000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6620000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6826000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7396000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7729000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8550000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9270000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9605000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11359000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11533000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11679000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11739000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11504000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11556000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11576000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12338000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12358000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12507000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12821000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>13004000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17728000</v>
+      </c>
+      <c r="E49" s="3">
         <v>17253000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17323000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>16023000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>16085000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>16134000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15974000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16033000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16111000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16136000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16201000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16255000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16298000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16375000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16435000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>16541000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>16576000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>16597000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>23131000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>23394000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>33435000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>33556000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>33658000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>34064000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>34213000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>34337000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>34472000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>34653000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>34694000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>34788000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>34845000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>34794000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4620,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,106 +4721,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4115000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4044000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4052000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4255000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4182000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4076000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3970000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4280000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4247000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4269000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4183000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3911000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4025000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4144000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4193000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4478000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4499000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5666000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6816000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7505000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7906000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7915000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7901000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6263000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6052000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6047000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5923000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5183000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>4971000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5277000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4882000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>4734000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,106 +4923,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>49373000</v>
+      </c>
+      <c r="E54" s="3">
         <v>47856000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>47957000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>45813000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>44826000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>43855000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>43135000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>44093000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>42827000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>41967000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>41511000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>41038000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>40908000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>42036000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>42434000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>44066000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>44667000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>48594000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>56312000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>57990000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>70591000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>70321000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>70507000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>70046000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>70156000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>71478000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>71987000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>73569000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>74862000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>76175000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>77956000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>80594000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5063,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,596 +5100,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10099000</v>
+      </c>
+      <c r="E57" s="3">
         <v>10051000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10904000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9222000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8938000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8700000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9121000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9034000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8528000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8638000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8382000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7615000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7635000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7956000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8442000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9201000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9824000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10168000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10663000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10364000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9851000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9702000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10223000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9419000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9367000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9598000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10036000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9676000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9413000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9380000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9939000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9378000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1033000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1430000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1123000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1998000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1993000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2140000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1632000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>899000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>901000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>923000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>909000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1025000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>36000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>749000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>850000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1292000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>603000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1233000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>524000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>340000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>98000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>99000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1407000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3215000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3736000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4586000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3324000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1289000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2224000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2449000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3153000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3739000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1277000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1398000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1368000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1308000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1232000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1412000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1265000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1201000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1154000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1135000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1068000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1095000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1113000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1168000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1199000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1158000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1238000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1861000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1911000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1779000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1824000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1896000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1856000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1966000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1963000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2011000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1922000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2049000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1890000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1947000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1967000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1855000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12409000</v>
+      </c>
+      <c r="E60" s="3">
         <v>12879000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13395000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12528000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12163000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12252000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12018000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11134000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10583000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10696000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10359000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9735000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8784000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9873000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10491000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11651000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11665000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13262000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13098000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12483000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11773000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11697000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>13486000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>14600000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>15066000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>16195000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>15282000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>13014000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>13527000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>13776000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>15059000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>14972000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12156000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10740000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10842000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11147000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11342000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10698000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10594000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12452000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12946000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13163000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13286000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>14370000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>15687000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>15834000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>16036000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>16471000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>16763000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>15409000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14770000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>16333000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>16978000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>16449000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14644000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>14159000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>13865000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>13526000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>14875000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>15871000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>16600000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>16538000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>16463000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>17538000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2528000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2314000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2361000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2431000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2387000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2525000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2534000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2996000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2673000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2469000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2580000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3268000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3378000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3357000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3418000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3575000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3783000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3940000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4268000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4847000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5567000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5651000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5791000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4339000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4328000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4431000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4569000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4674000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4783000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4807000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4905000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5510000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5805,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5754,8 +5906,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,106 +6007,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>28302000</v>
+      </c>
+      <c r="E66" s="3">
         <v>27120000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>27768000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26427000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>26218000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25787000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25450000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26894000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26502000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>26620000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26507000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27676000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28146000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>29493000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>30363000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>32125000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>32627000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>33033000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>32552000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>34077000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>34739000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>34218000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>34345000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>33513000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>33672000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>34554000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>35145000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>33996000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>35342000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>35569000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>36878000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>38360000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6147,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6246,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6347,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6448,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,106 +6549,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14890000</v>
+      </c>
+      <c r="E72" s="3">
         <v>14172000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13497000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12742000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11974000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11296000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10719000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9904000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9244000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8532000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8199000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7775000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7399000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7142000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7018000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6818000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7073000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>10681000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>18751000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>19111000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>31186000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>31386000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>31658000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>31712000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>31760000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>32022000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>32190000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>35136000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>35284000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>36052000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>36470000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>37370000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6751,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6852,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,106 +6953,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21071000</v>
+      </c>
+      <c r="E76" s="3">
         <v>20736000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20189000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>19386000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18608000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18068000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17685000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17199000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16325000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15347000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15004000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13362000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12762000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12543000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12071000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11941000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12040000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15561000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>23760000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>23913000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>35852000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>36103000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>36162000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>36533000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>36484000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>36924000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>36842000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>39573000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>39520000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>40606000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>41078000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>42234000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7155,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1112000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1068000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1112000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1123000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1033000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>934000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1064000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>907000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>959000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>510000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>601000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>550000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>431000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>299000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>374000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-82000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3434000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7376000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>333000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-11383000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>492000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>421000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>539000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>644000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>430000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>525000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>545000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-74000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>279000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-205000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,106 +7401,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>631000</v>
+      </c>
+      <c r="E83" s="3">
         <v>600000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>609000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>579000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>561000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>563000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>549000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>533000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>532000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>533000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>532000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>530000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>526000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>532000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>583000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>587000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>604000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>792000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>848000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>900000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>938000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>903000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>919000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>887000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>876000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>874000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>906000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>956000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>986000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>989000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1016000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>998000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7601,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7702,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7803,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7904,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,106 +8005,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1436000</v>
+      </c>
+      <c r="E89" s="3">
         <v>327000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3022000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1677000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1608000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>330000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1614000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1567000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>408000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>131000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1932000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1070000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1220000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>429000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>878000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>479000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>803000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>784000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2252000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1745000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1108000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>326000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2331000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1827000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>987000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>568000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2251000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1898000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>858000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>656000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2013000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1406000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,106 +8145,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-463000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-399000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-594000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-464000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-471000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-410000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-572000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-382000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-360000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-304000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-447000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-273000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-243000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-178000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-258000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-251000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-407000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-494000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-413000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-404000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-413000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-621000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-565000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-520000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-454000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-625000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-598000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-503000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-381000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-654000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-403000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8345,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,106 +8446,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1493000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-151000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-520000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-733000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-983000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-547000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-272000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1083000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>82000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-115000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-526000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-619000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>15000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>211000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>246000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-740000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-547000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1312000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-203000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-934000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-644000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-230000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-315000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-895000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-112000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>282000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>221000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>473000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-55000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-32000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,16 +8586,17 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-394000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-357000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-356000</v>
       </c>
       <c r="F96" s="3">
         <v>-356000</v>
@@ -8371,19 +8605,19 @@
         <v>-356000</v>
       </c>
       <c r="H96" s="3">
+        <v>-356000</v>
+      </c>
+      <c r="I96" s="3">
         <v>-249000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-248000</v>
       </c>
       <c r="J96" s="3">
         <v>-248000</v>
       </c>
       <c r="K96" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="L96" s="3">
         <v>-177000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-175000</v>
       </c>
       <c r="M96" s="3">
         <v>-175000</v>
@@ -8395,7 +8629,7 @@
         <v>-175000</v>
       </c>
       <c r="P96" s="3">
-        <v>-174000</v>
+        <v>-175000</v>
       </c>
       <c r="Q96" s="3">
         <v>-174000</v>
@@ -8404,10 +8638,10 @@
         <v>-174000</v>
       </c>
       <c r="S96" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-694000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-692000</v>
       </c>
       <c r="U96" s="3">
         <v>-692000</v>
@@ -8416,34 +8650,34 @@
         <v>-692000</v>
       </c>
       <c r="W96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-693000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-692000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-693000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-692000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-693000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-692000</v>
       </c>
       <c r="AC96" s="3">
         <v>-692000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-697000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-696000</v>
       </c>
       <c r="AG96" s="3">
         <v>-696000</v>
@@ -8451,8 +8685,11 @@
       <c r="AH96" s="3">
         <v>-696000</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>-696000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8786,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8887,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,298 +8988,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>221000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-267000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2009000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-382000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-183000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>62000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1844000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-180000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-188000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-170000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1220000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-322000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1070000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-212000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1504000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>21000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-167000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>777000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2097000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1090000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-234000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-297000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2069000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-900000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1264000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-787000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>278000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2342000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1332000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1637000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2389000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1116000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-21000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-81000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-13000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-23000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-17000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>6000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>5000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-11000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>6000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>3000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>10000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>9000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-104000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-112000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>412000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>558000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>429000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-154000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-525000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>287000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>293000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-157000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>188000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>130000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>171000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>424000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-375000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-243000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>87000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>238000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-46000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-283000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>236000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-203000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-60000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>32000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-404000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>66000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>109000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-213000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1027000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-512000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>494000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>SLB</t>
   </si>
@@ -656,455 +656,468 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9159000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9139000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8707000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8990000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8310000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8099000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7736000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7878000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7477000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6773000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5962000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6225000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5847000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5634000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5223000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5532000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5258000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5356000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7455000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8228000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8541000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8269000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7879000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8179000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8504000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8303000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>7829000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8179000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7905000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7462000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6894000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7107000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7019000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7237000</v>
+      </c>
+      <c r="E9" s="3">
         <v>7247000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6993000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7183000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6592000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6502000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6285000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6307000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6042000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5568000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5013000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5136000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4862000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4768000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4504000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4828000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4624000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4925000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6614000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7136000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7382000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7236000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6956000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7193000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7305000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>7184000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>6834000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>7169000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6787000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6469000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>6082000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>6113000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6114000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1922000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1892000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1714000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1807000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1718000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1597000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1451000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1571000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1435000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1205000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>949000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1089000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>985000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>866000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>719000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>704000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>634000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>431000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>841000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1092000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1159000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1033000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>923000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>986000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1199000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1119000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>995000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1010000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1118000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>993000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>812000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>994000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>905000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1140,109 +1153,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>187000</v>
+      </c>
+      <c r="E12" s="3">
         <v>188000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>182000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>187000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>186000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>163000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>174000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>178000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>160000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>154000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>141000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>145000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>140000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>134000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>135000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>128000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>137000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>142000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>173000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>190000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>176000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>179000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>173000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>178000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>177000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>175000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>172000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>192000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>189000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>196000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>211000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>262000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1342,47 +1359,50 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E14" s="3">
         <v>142000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>25000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>56000</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="3">
         <v>-36000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-83000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-216000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-26000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-28000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1390,84 +1410,87 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-42000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>350000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3724000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>8523000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>209000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>12692000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-43000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>184000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>2796000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>49000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>591000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>82000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>676000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>237000</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>640000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>631000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>579000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>561000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>563000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1544,8 +1567,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1578,210 +1604,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>7671000</v>
+        <v>7514000</v>
       </c>
       <c r="E17" s="3">
-        <v>7321000</v>
+        <v>7529000</v>
       </c>
       <c r="F17" s="3">
-        <v>7522000</v>
+        <v>7296000</v>
       </c>
       <c r="G17" s="3">
+        <v>7466000</v>
+      </c>
+      <c r="H17" s="3">
         <v>6859000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6761000</v>
       </c>
-      <c r="I17" s="3">
-        <v>6514000</v>
-      </c>
       <c r="J17" s="3">
+        <v>6550000</v>
+      </c>
+      <c r="K17" s="3">
         <v>6501000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6296000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5592000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5225000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5361000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5082000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4972000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4720000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4986000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5196000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8872000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15437000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7664000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>20370000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7529000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7241000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7442000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7587000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7657000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7117000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10266000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7140000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7366000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6473000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7149000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6696000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1468000</v>
+        <v>1645000</v>
       </c>
       <c r="E18" s="3">
-        <v>1386000</v>
+        <v>1610000</v>
       </c>
       <c r="F18" s="3">
-        <v>1468000</v>
+        <v>1411000</v>
       </c>
       <c r="G18" s="3">
+        <v>1524000</v>
+      </c>
+      <c r="H18" s="3">
         <v>1451000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1338000</v>
       </c>
-      <c r="I18" s="3">
-        <v>1222000</v>
-      </c>
       <c r="J18" s="3">
+        <v>1186000</v>
+      </c>
+      <c r="K18" s="3">
         <v>1377000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>1181000</v>
       </c>
       <c r="L18" s="3">
         <v>1181000</v>
       </c>
       <c r="M18" s="3">
+        <v>1181000</v>
+      </c>
+      <c r="N18" s="3">
         <v>737000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>864000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>765000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>662000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>503000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>546000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>62000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3516000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7982000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>564000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-11829000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>740000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>638000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>737000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>917000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>646000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>712000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2087000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>765000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>96000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>421000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-42000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>323000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1817,513 +1850,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>85000</v>
+        <v>-44000</v>
       </c>
       <c r="E20" s="3">
-        <v>84000</v>
+        <v>-47000</v>
       </c>
       <c r="F20" s="3">
+        <v>-46000</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>91000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>75000</v>
+      </c>
+      <c r="M20" s="3">
         <v>95000</v>
       </c>
-      <c r="G20" s="3">
-        <v>73000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>82000</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="N20" s="3">
+        <v>24000</v>
+      </c>
+      <c r="O20" s="3">
+        <v>29000</v>
+      </c>
+      <c r="P20" s="3">
         <v>56000</v>
       </c>
-      <c r="J20" s="3">
-        <v>91000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>75000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>95000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>24000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>29000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>56000</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>16000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>19000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>69000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>22000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-59000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-29000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>30000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>20000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>31000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>34000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>16000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>41000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>48000</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>28000</v>
       </c>
       <c r="AD20" s="3">
         <v>28000</v>
       </c>
       <c r="AE20" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AF20" s="3">
         <v>73000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>92000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>70000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-73000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>2184000</v>
+        <v>2329000</v>
       </c>
       <c r="E21" s="3">
-        <v>2070000</v>
+        <v>2288000</v>
       </c>
       <c r="F21" s="3">
-        <v>2172000</v>
+        <v>2057000</v>
       </c>
       <c r="G21" s="3">
-        <v>2103000</v>
+        <v>1634000</v>
       </c>
       <c r="H21" s="3">
-        <v>1981000</v>
+        <v>2030000</v>
       </c>
       <c r="I21" s="3">
-        <v>1841000</v>
+        <v>1899000</v>
       </c>
       <c r="J21" s="3">
+        <v>1788000</v>
+      </c>
+      <c r="K21" s="3">
         <v>2017000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1789000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1808000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1294000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1425000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1351000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1204000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1054000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1198000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>671000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2971000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-7219000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1442000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-10909000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1709000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1575000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1672000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1845000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1570000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1614000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1153000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1794000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1174000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1480000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>901000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1352000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E22" s="3">
         <v>132000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>113000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>130000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>129000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>127000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>117000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>121000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>122000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>124000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>123000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>137000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>130000</v>
-      </c>
-      <c r="P22" s="3">
-        <v>136000</v>
       </c>
       <c r="Q22" s="3">
         <v>136000</v>
       </c>
       <c r="R22" s="3">
+        <v>136000</v>
+      </c>
+      <c r="S22" s="3">
         <v>144000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>138000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>52000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>78000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>142000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>162000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>178000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>163000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>105000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>171000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>147000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>97000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>151000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>161000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>171000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>157000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>99000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1507000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1421000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1357000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1433000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1395000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1293000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1161000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1347000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1134000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1152000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>638000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>756000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>691000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>542000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>386000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>471000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-54000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3627000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8089000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>452000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11971000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>593000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>509000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>648000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>787000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>547000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>643000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2210000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>677000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>17000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>334000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-214000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>200000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>289000</v>
+      </c>
+      <c r="E24" s="3">
         <v>276000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>259000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>285000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>259000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>246000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>217000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>265000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>215000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>182000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>118000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>145000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>129000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>99000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>74000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>89000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>19000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-199000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-721000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>109000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-598000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>99000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>79000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>99000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>129000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>106000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>113000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>121000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>98000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>50000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-19000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2423,210 +2472,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1218000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1145000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1098000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1148000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1136000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1047000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>944000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1082000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>919000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>970000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>520000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>611000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>562000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>443000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>312000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>382000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-73000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3428000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7368000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>343000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11373000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>494000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>430000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>549000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>658000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>441000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>530000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2195000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>556000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-81000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>284000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-195000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>190000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1186000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1112000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1068000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1112000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1123000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1033000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>934000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1064000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>907000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>959000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>510000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>601000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>550000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>431000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>299000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>374000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-82000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3434000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7376000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>333000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-11383000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>492000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>421000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>539000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>644000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>430000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>525000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2178000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>545000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-74000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>279000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-205000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2726,8 +2784,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2791,8 +2852,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>24</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>24</v>
@@ -2809,11 +2870,11 @@
       <c r="AC29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-76000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>24</v>
@@ -2821,14 +2882,17 @@
       <c r="AG29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="3" t="s">
+      <c r="AH29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2928,8 +2992,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3029,210 +3096,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-85000</v>
+        <v>44000</v>
       </c>
       <c r="E32" s="3">
-        <v>-84000</v>
+        <v>47000</v>
       </c>
       <c r="F32" s="3">
+        <v>46000</v>
+      </c>
+      <c r="G32" s="3">
+        <v>54000</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J32" s="3">
+        <v>39000</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-91000</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="M32" s="3">
         <v>-95000</v>
       </c>
-      <c r="G32" s="3">
-        <v>-73000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-82000</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="N32" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="P32" s="3">
         <v>-56000</v>
       </c>
-      <c r="J32" s="3">
-        <v>-91000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-75000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-95000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-24000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-29000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-56000</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-19000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-69000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-22000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>59000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>29000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-30000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-20000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-31000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-34000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-48000</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-28000</v>
       </c>
       <c r="AD32" s="3">
         <v>-28000</v>
       </c>
       <c r="AE32" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-73000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-92000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-70000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>73000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-31000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1186000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1112000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1068000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1112000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1123000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1033000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>934000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1064000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>907000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>959000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>510000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>601000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>550000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>431000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>299000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>374000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-82000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3434000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7376000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>333000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-11383000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>492000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>421000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>539000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>644000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>430000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>525000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>545000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-74000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>279000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-205000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3332,215 +3408,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1186000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1112000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1068000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1112000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1123000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1033000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>934000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1064000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>907000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>959000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>510000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>601000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>550000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>431000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>299000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>374000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-82000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3434000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7376000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>333000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-11383000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>492000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>421000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>539000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>644000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>430000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>525000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>545000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-74000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>279000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-205000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3576,8 +3661,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3613,917 +3699,945 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3086000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2953000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2788000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2900000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2488000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1930000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1501000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1655000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2180000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1893000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1600000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1757000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1569000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1439000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1268000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>844000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1219000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1462000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1375000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1137000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1183000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1466000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1230000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1433000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1493000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1461000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1865000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1799000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1690000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1903000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1902000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2929000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3441000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1387000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1050000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>703000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1089000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1247000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1264000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1003000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1239000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1429000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>923000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1049000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1382000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1373000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1243000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1642000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2162000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2618000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2127000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1969000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1030000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1109000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>882000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>925000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1344000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1361000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1588000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2300000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>3290000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>3262000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>4315000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>5451000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>6328000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>7315000</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8260000</v>
+      </c>
+      <c r="E43" s="3">
         <v>8605000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8222000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7812000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8049000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7675000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7578000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7032000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6650000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6247000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5713000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5315000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5349000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5347000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5269000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5247000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5552000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5808000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7486000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7747000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>8332000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8471000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8171000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7881000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8409000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8606000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8472000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8084000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>9436000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>8925000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8636000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>9387000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>9565000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4573000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4504000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4549000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4387000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4305000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4360000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4286000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3999000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4143000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3968000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3719000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3272000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3296000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3267000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3303000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3354000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3542000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3601000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4148000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4130000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4341000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4389000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4224000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4010000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4108000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4120000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4174000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4046000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4308000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4338000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4288000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4225000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4572000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1495000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1405000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1438000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1530000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>949000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>925000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1032000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1078000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1209000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1285000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1172000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>928000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>800000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>781000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1325000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1312000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1284000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1381000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1288000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1486000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1186000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1125000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1223000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1063000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1112000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1125000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1244000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1278000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1218000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1792000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1606000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1058000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1532000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18801000</v>
+      </c>
+      <c r="E46" s="3">
         <v>18517000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17700000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17718000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17038000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16154000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15400000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15003000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15611000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14316000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13253000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12654000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12387000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12077000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12807000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12919000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>14215000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>14379000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>16266000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>15530000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>16151000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>16333000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>15773000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>15731000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16483000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16900000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>18055000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>18497000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>19914000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>21273000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>21883000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>23927000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>26425000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1678000</v>
+        <v>1783000</v>
       </c>
       <c r="E47" s="3">
-        <v>1606000</v>
+        <v>1690000</v>
       </c>
       <c r="F47" s="3">
-        <v>1624000</v>
+        <v>1623000</v>
       </c>
       <c r="G47" s="3">
-        <v>1622000</v>
+        <v>3735000</v>
       </c>
       <c r="H47" s="3">
-        <v>1601000</v>
+        <v>1634000</v>
       </c>
       <c r="I47" s="3">
-        <v>1554000</v>
+        <v>1612000</v>
       </c>
       <c r="J47" s="3">
+        <v>1561000</v>
+      </c>
+      <c r="K47" s="3">
         <v>1581000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1762000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1767000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1955000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2044000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2110000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2035000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2090000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2061000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1436000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1484000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1515000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1565000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1335000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1558000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1544000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1538000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1497000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1487000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1483000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1519000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1566000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1720000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1637000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7360000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7335000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7253000</v>
       </c>
-      <c r="F48" s="3">
-        <v>7240000</v>
-      </c>
       <c r="G48" s="3">
+        <v>7958000</v>
+      </c>
+      <c r="H48" s="3">
         <v>6875000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6804000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6691000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6607000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6407000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6386000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6354000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6429000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6375000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6473000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6620000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6826000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7396000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7729000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8550000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9270000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9605000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11359000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11533000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11679000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11739000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11504000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11556000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11576000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12338000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12358000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12507000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12821000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>13004000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17681000</v>
+      </c>
+      <c r="E49" s="3">
         <v>17728000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17253000</v>
       </c>
-      <c r="F49" s="3">
-        <v>17323000</v>
-      </c>
       <c r="G49" s="3">
+        <v>17474000</v>
+      </c>
+      <c r="H49" s="3">
         <v>16023000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>16085000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16134000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15974000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16033000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16111000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16136000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16201000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16255000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16298000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16375000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>16435000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>16541000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>16576000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>16597000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>23131000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>23394000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>33435000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>33556000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>33658000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>34064000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>34213000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>34337000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>34472000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>34653000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>34694000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>34788000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>34845000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>34794000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4623,8 +4737,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4724,109 +4841,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4115000</v>
+        <v>4150000</v>
       </c>
       <c r="E52" s="3">
-        <v>4044000</v>
+        <v>4103000</v>
       </c>
       <c r="F52" s="3">
-        <v>4052000</v>
+        <v>4027000</v>
       </c>
       <c r="G52" s="3">
-        <v>4255000</v>
+        <v>1072000</v>
       </c>
       <c r="H52" s="3">
-        <v>4182000</v>
+        <v>4243000</v>
       </c>
       <c r="I52" s="3">
-        <v>4076000</v>
+        <v>4171000</v>
       </c>
       <c r="J52" s="3">
+        <v>4069000</v>
+      </c>
+      <c r="K52" s="3">
         <v>3970000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4280000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4247000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4269000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4183000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3911000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4025000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4144000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4193000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4478000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4499000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5666000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6816000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7505000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7906000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7915000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7901000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6263000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6052000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6047000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5923000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5183000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>4971000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5277000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>4882000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>4734000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4926,109 +5049,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>49775000</v>
+      </c>
+      <c r="E54" s="3">
         <v>49373000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>47856000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>47957000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>45813000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>44826000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>43855000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>43135000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>44093000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>42827000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>41967000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>41511000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>41038000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>40908000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>42036000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>42434000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>44066000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>44667000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>48594000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>56312000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>57990000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>70591000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>70321000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>70507000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>70046000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>70156000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>71478000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>71987000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>73569000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>74862000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>76175000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>77956000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>80594000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5064,8 +5193,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5101,614 +5231,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>10099000</v>
+        <v>8346000</v>
       </c>
       <c r="E57" s="3">
-        <v>10051000</v>
+        <v>8082000</v>
       </c>
       <c r="F57" s="3">
-        <v>10904000</v>
+        <v>8040000</v>
       </c>
       <c r="G57" s="3">
-        <v>9222000</v>
+        <v>4613000</v>
       </c>
       <c r="H57" s="3">
-        <v>8938000</v>
+        <v>7922000</v>
       </c>
       <c r="I57" s="3">
-        <v>8700000</v>
+        <v>7638000</v>
       </c>
       <c r="J57" s="3">
+        <v>7497000</v>
+      </c>
+      <c r="K57" s="3">
         <v>9121000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9034000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8528000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8638000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8382000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7615000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7635000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7956000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8442000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9201000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9824000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10168000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10663000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10364000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9851000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9702000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10223000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9419000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9367000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9598000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10036000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9676000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9413000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9380000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9939000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9378000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1033000</v>
+        <v>1059000</v>
       </c>
       <c r="E58" s="3">
-        <v>1430000</v>
+        <v>1050000</v>
       </c>
       <c r="F58" s="3">
-        <v>1123000</v>
+        <v>1441000</v>
       </c>
       <c r="G58" s="3">
+        <v>1331000</v>
+      </c>
+      <c r="H58" s="3">
         <v>1998000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1993000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2140000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1632000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>899000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>901000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>923000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>909000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1025000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>36000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>749000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>850000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1292000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>603000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1233000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>524000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>340000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>98000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>99000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1407000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3215000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3736000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4586000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3324000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1289000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2224000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2449000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3153000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3739000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1277000</v>
+        <v>3294000</v>
       </c>
       <c r="E59" s="3">
-        <v>1398000</v>
+        <v>3277000</v>
       </c>
       <c r="F59" s="3">
-        <v>1368000</v>
+        <v>3398000</v>
       </c>
       <c r="G59" s="3">
-        <v>1308000</v>
+        <v>5826000</v>
       </c>
       <c r="H59" s="3">
-        <v>1232000</v>
+        <v>2608000</v>
       </c>
       <c r="I59" s="3">
-        <v>1412000</v>
+        <v>2532000</v>
       </c>
       <c r="J59" s="3">
+        <v>2615000</v>
+      </c>
+      <c r="K59" s="3">
         <v>1265000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1201000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1154000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1135000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1068000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1095000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1113000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1168000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1199000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1158000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1238000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1861000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1911000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1779000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1824000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1896000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1856000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1966000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1963000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2011000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1922000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2049000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1890000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1947000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1967000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1855000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12699000</v>
+      </c>
+      <c r="E60" s="3">
         <v>12409000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12879000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13395000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12528000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12163000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12252000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12018000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11134000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10583000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10696000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10359000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9735000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8784000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9873000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10491000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11651000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11665000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13262000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>13098000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12483000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11773000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11697000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>13486000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>14600000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>15066000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>16195000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>15282000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>13014000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>13527000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>13776000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>15059000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>14972000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>12156000</v>
+        <v>11928000</v>
       </c>
       <c r="E61" s="3">
-        <v>10740000</v>
+        <v>12314000</v>
       </c>
       <c r="F61" s="3">
-        <v>10842000</v>
+        <v>10838000</v>
       </c>
       <c r="G61" s="3">
-        <v>11147000</v>
+        <v>11511000</v>
       </c>
       <c r="H61" s="3">
-        <v>11342000</v>
+        <v>11388000</v>
       </c>
       <c r="I61" s="3">
-        <v>10698000</v>
+        <v>11497000</v>
       </c>
       <c r="J61" s="3">
+        <v>10981000</v>
+      </c>
+      <c r="K61" s="3">
         <v>10594000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12452000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12946000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13163000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13286000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>14370000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>15687000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>15834000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>16036000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>16471000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>16763000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>15409000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>14770000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>16333000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>16978000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>16449000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>14644000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>14159000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>13865000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>13526000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>14875000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>15871000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>16600000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>16538000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>16463000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>17538000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2528000</v>
+        <v>2073000</v>
       </c>
       <c r="E62" s="3">
-        <v>2314000</v>
+        <v>2060000</v>
       </c>
       <c r="F62" s="3">
-        <v>2361000</v>
+        <v>1924000</v>
       </c>
       <c r="G62" s="3">
-        <v>2431000</v>
+        <v>1377000</v>
       </c>
       <c r="H62" s="3">
-        <v>2387000</v>
+        <v>1867000</v>
       </c>
       <c r="I62" s="3">
-        <v>2525000</v>
+        <v>1882000</v>
       </c>
       <c r="J62" s="3">
+        <v>1880000</v>
+      </c>
+      <c r="K62" s="3">
         <v>2534000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2996000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2673000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2469000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2580000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3268000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3378000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3357000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3418000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3575000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3783000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3940000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4268000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4847000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5567000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5651000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>5791000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4339000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4328000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4431000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4569000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4674000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4783000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4807000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4905000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5510000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5808,8 +5957,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5909,8 +6061,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6010,109 +6165,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>28302000</v>
+        <v>27047000</v>
       </c>
       <c r="E66" s="3">
-        <v>27120000</v>
+        <v>27093000</v>
       </c>
       <c r="F66" s="3">
-        <v>27768000</v>
+        <v>25933000</v>
       </c>
       <c r="G66" s="3">
-        <v>26427000</v>
+        <v>26598000</v>
       </c>
       <c r="H66" s="3">
-        <v>26218000</v>
+        <v>26106000</v>
       </c>
       <c r="I66" s="3">
-        <v>25787000</v>
+        <v>25892000</v>
       </c>
       <c r="J66" s="3">
+        <v>25475000</v>
+      </c>
+      <c r="K66" s="3">
         <v>25450000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26894000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>26502000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26620000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26507000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>27676000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28146000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>29493000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>30363000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>32125000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>32627000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>33033000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>32552000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>34077000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>34739000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>34218000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>34345000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>33513000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>33672000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>34554000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>35145000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>33996000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>35342000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>35569000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>36878000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>38360000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6148,8 +6309,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6249,8 +6411,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6350,8 +6515,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6451,8 +6619,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6552,109 +6723,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15687000</v>
+      </c>
+      <c r="E72" s="3">
         <v>14890000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>14172000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13497000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12742000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11974000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11296000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10719000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9904000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9244000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8532000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8199000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7775000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7399000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7142000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7018000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6818000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7073000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>10681000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>18751000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>19111000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>31186000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>31386000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>31658000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>31712000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>31760000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>32022000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>32190000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>35136000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>35284000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>36052000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>36470000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>37370000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6754,8 +6931,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6855,8 +7035,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6956,109 +7139,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21511000</v>
+      </c>
+      <c r="E76" s="3">
         <v>21071000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20736000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20189000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>19386000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18608000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18068000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17685000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17199000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16325000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15347000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15004000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13362000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12762000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12543000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12071000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11941000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12040000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15561000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>23760000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>23913000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>35852000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>36103000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>36162000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>36533000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>36484000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>36924000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>36842000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>39573000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>39520000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>40606000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>41078000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>42234000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7158,215 +7347,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1186000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1112000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1068000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1112000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1123000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1033000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>934000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1064000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>907000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>959000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>510000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>601000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>550000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>431000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>299000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>374000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-82000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3434000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7376000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>333000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-11383000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>492000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>421000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>539000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>644000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>430000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>525000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>545000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-74000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>279000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-205000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7402,109 +7600,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>631000</v>
+        <v>501000</v>
       </c>
       <c r="E83" s="3">
-        <v>600000</v>
+        <v>484000</v>
       </c>
       <c r="F83" s="3">
-        <v>609000</v>
+        <v>487000</v>
       </c>
       <c r="G83" s="3">
-        <v>579000</v>
+        <v>71000</v>
       </c>
       <c r="H83" s="3">
-        <v>561000</v>
+        <v>457000</v>
       </c>
       <c r="I83" s="3">
-        <v>563000</v>
+        <v>457000</v>
       </c>
       <c r="J83" s="3">
+        <v>458000</v>
+      </c>
+      <c r="K83" s="3">
         <v>549000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>533000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>532000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>533000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>532000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>530000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>526000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>532000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>583000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>587000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>604000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>792000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>848000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>900000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>938000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>903000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>919000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>887000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>876000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>874000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>906000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>956000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>986000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>989000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1016000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>998000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7604,8 +7806,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7705,8 +7910,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7806,8 +8014,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7907,8 +8118,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8008,109 +8222,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2449000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1436000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>327000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3022000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1677000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1608000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>330000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1614000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1567000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>408000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>131000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1932000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1070000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1220000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>429000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>878000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>479000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>803000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>784000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2252000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1745000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1108000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>326000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2331000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1827000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>987000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>568000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2251000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1898000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>858000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>656000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2013000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1406000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8146,109 +8366,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-463000</v>
+        <v>-594000</v>
       </c>
       <c r="E91" s="3">
-        <v>-399000</v>
+        <v>-598000</v>
       </c>
       <c r="F91" s="3">
-        <v>-594000</v>
+        <v>-520000</v>
       </c>
       <c r="G91" s="3">
-        <v>-464000</v>
+        <v>-710000</v>
       </c>
       <c r="H91" s="3">
-        <v>-471000</v>
+        <v>-602000</v>
       </c>
       <c r="I91" s="3">
-        <v>-410000</v>
+        <v>-591000</v>
       </c>
       <c r="J91" s="3">
+        <v>-543000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-572000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-382000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-360000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-304000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-447000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-273000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-243000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-178000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-258000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-251000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-407000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-494000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-413000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-404000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-413000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-621000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-565000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-520000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-454000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-625000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-598000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-503000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-381000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-654000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-403000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8348,8 +8572,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8449,109 +8676,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1024000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1493000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-151000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-520000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-733000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-983000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-547000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-272000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1083000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>82000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-115000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-526000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-619000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>15000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>211000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>246000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-740000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-547000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1312000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-203000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-934000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-644000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-230000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-315000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-895000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-112000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>282000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>221000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>473000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-55000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-32000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8587,40 +8820,41 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-394000</v>
+        <v>393000</v>
       </c>
       <c r="E96" s="3">
-        <v>-357000</v>
+        <v>394000</v>
       </c>
       <c r="F96" s="3">
-        <v>-356000</v>
+        <v>357000</v>
       </c>
       <c r="G96" s="3">
-        <v>-356000</v>
+        <v>356000</v>
       </c>
       <c r="H96" s="3">
-        <v>-356000</v>
+        <v>356000</v>
       </c>
       <c r="I96" s="3">
-        <v>-249000</v>
+        <v>356000</v>
       </c>
       <c r="J96" s="3">
-        <v>-248000</v>
+        <v>249000</v>
       </c>
       <c r="K96" s="3">
         <v>-248000</v>
       </c>
       <c r="L96" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="M96" s="3">
         <v>-177000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-175000</v>
       </c>
       <c r="N96" s="3">
         <v>-175000</v>
@@ -8632,7 +8866,7 @@
         <v>-175000</v>
       </c>
       <c r="Q96" s="3">
-        <v>-174000</v>
+        <v>-175000</v>
       </c>
       <c r="R96" s="3">
         <v>-174000</v>
@@ -8641,10 +8875,10 @@
         <v>-174000</v>
       </c>
       <c r="T96" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-694000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-692000</v>
       </c>
       <c r="V96" s="3">
         <v>-692000</v>
@@ -8653,34 +8887,34 @@
         <v>-692000</v>
       </c>
       <c r="X96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-693000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-692000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-692000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-693000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-692000</v>
       </c>
       <c r="AD96" s="3">
         <v>-692000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-697000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-696000</v>
       </c>
       <c r="AH96" s="3">
         <v>-696000</v>
@@ -8688,8 +8922,11 @@
       <c r="AI96" s="3">
         <v>-696000</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>-696000</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8789,8 +9026,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8890,8 +9130,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8991,307 +9234,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1295000</v>
+      </c>
+      <c r="E100" s="3">
         <v>221000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-267000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2009000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-382000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-183000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>62000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1844000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-180000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-188000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-170000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1220000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-322000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1070000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-212000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1504000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>21000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-167000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>777000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2097000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1090000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-234000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-297000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2069000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-900000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1264000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-787000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>278000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2342000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1332000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1637000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2389000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1116000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="F101" s="3">
         <v>1000</v>
       </c>
-      <c r="E101" s="3">
-        <v>-21000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-81000</v>
-      </c>
       <c r="G101" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="O101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="R101" s="3">
         <v>-4000</v>
       </c>
-      <c r="H101" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="I101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-23000</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-17000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-9000</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="S101" s="3">
+        <v>5000</v>
+      </c>
+      <c r="T101" s="3">
         <v>-3000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="U101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="W101" s="3">
         <v>2000</v>
       </c>
-      <c r="O101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="X101" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="Y101" s="3">
         <v>6000</v>
       </c>
-      <c r="Q101" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="R101" s="3">
-        <v>5000</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="Z101" s="3">
         <v>-2000</v>
       </c>
-      <c r="U101" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="AA101" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>10000</v>
+      </c>
+      <c r="AG101" s="3">
         <v>2000</v>
       </c>
-      <c r="W101" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="X101" s="3">
-        <v>6000</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>10000</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>9000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-104000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E102" s="3">
         <v>165000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-112000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>412000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>558000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>429000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-154000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-525000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>287000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>293000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-157000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>188000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>130000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>171000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>424000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-375000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-243000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>87000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>238000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-46000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-283000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>236000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-203000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-60000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>32000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-404000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>66000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>109000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-213000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1027000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-512000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>494000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
@@ -656,468 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9284000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9159000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9139000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8707000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8990000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8310000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8099000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7736000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7878000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7477000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6773000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5962000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6225000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5847000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5634000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5223000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5532000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5258000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5356000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7455000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8228000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8541000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8269000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7879000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8179000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8504000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8303000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7829000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8179000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7905000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7462000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6894000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7107000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7019000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7323000</v>
+      </c>
+      <c r="E9" s="3">
         <v>7237000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7247000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6993000</v>
       </c>
-      <c r="G9" s="3">
-        <v>7183000</v>
-      </c>
       <c r="H9" s="3">
+        <v>7093000</v>
+      </c>
+      <c r="I9" s="3">
         <v>6592000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6502000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6285000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6307000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6042000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5568000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5013000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5136000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4862000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4768000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4504000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4828000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4624000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4925000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6614000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7136000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7382000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7236000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6956000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7193000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>7305000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>7184000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6834000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7169000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6787000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>6469000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>6082000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6113000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>6114000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1961000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1922000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1892000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1714000</v>
       </c>
-      <c r="G10" s="3">
-        <v>1807000</v>
-      </c>
       <c r="H10" s="3">
+        <v>1897000</v>
+      </c>
+      <c r="I10" s="3">
         <v>1718000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1597000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1451000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1571000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1435000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1205000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>949000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1089000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>985000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>866000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>719000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>704000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>634000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>431000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>841000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1092000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1159000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1033000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>923000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>986000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1199000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1119000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>995000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1010000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1118000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>993000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>812000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>994000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>905000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1154,112 +1166,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>192000</v>
+      </c>
+      <c r="E12" s="3">
         <v>187000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>188000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>182000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>187000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>186000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>163000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>174000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>178000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>160000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>154000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>141000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>145000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>140000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>134000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>135000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>128000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>137000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>142000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>173000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>190000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>176000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>179000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>173000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>178000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>177000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>175000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>172000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>192000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>189000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>196000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>211000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>262000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1362,50 +1378,53 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>262000</v>
+      </c>
+      <c r="E14" s="3">
         <v>98000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>142000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>25000</v>
       </c>
-      <c r="G14" s="3">
-        <v>56000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>24</v>
+      <c r="H14" s="3">
+        <v>146000</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="3">
         <v>-36000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-83000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-216000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-26000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-28000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1413,88 +1432,91 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-42000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>350000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3724000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>8523000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>209000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>12692000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-43000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>184000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>2796000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>49000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>591000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>82000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>676000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>237000</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E15" s="3">
         <v>640000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>631000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>600000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>56000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>579000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>561000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>563000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1570,8 +1592,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1605,216 +1630,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7595000</v>
+      </c>
+      <c r="E17" s="3">
         <v>7514000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7529000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7296000</v>
       </c>
-      <c r="G17" s="3">
-        <v>7466000</v>
-      </c>
       <c r="H17" s="3">
+        <v>7376000</v>
+      </c>
+      <c r="I17" s="3">
         <v>6859000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6761000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6550000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6501000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6296000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5592000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5225000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5361000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5082000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4972000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4720000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4986000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5196000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8872000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15437000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7664000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>20370000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7529000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7241000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7442000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7587000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7657000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7117000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10266000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7140000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7366000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6473000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>7149000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6696000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1689000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1645000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1610000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1411000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1524000</v>
-      </c>
       <c r="H18" s="3">
+        <v>1614000</v>
+      </c>
+      <c r="I18" s="3">
         <v>1451000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1338000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1186000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1377000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>1181000</v>
       </c>
       <c r="M18" s="3">
         <v>1181000</v>
       </c>
       <c r="N18" s="3">
+        <v>1181000</v>
+      </c>
+      <c r="O18" s="3">
         <v>737000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>864000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>765000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>662000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>503000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>546000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>62000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3516000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7982000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>564000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-11829000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>740000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>638000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>737000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>917000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>646000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>712000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2087000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>765000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>96000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>421000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-42000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>323000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1851,528 +1883,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-46000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-44000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-47000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-46000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-54000</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3">
         <v>-39000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>91000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>75000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>95000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>24000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>29000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>56000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>16000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>19000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>69000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>22000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-59000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-29000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>30000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>20000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>31000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>34000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>16000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>41000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>48000</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>28000</v>
       </c>
       <c r="AE20" s="3">
         <v>28000</v>
       </c>
       <c r="AF20" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AG20" s="3">
         <v>73000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>92000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>70000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-73000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1749000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2329000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2288000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2057000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1634000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1724000</v>
+      </c>
+      <c r="I21" s="3">
         <v>2030000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1899000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1788000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2017000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1789000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1808000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1294000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1425000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1351000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1204000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1054000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1198000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>671000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2971000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-7219000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1442000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-10909000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1709000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1575000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1672000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1845000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1570000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1614000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-1153000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1794000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1174000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1480000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>901000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1352000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E22" s="3">
         <v>136000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>132000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>113000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>130000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>129000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>127000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>117000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>121000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>122000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>124000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>123000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>137000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>130000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>136000</v>
       </c>
       <c r="R22" s="3">
         <v>136000</v>
       </c>
       <c r="S22" s="3">
+        <v>136000</v>
+      </c>
+      <c r="T22" s="3">
         <v>144000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>138000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>52000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>78000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>142000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>162000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>178000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>163000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>105000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>171000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>147000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>97000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>151000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>161000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>171000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>157000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>99000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1387000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1507000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1421000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1357000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1433000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1395000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1293000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1161000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1347000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1134000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1152000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>638000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>756000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>691000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>542000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>386000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>471000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-54000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3627000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8089000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>452000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11971000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>593000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>509000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>648000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>787000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>547000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>643000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2210000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>677000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>17000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>334000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-214000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>200000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>269000</v>
+      </c>
+      <c r="E24" s="3">
         <v>289000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>276000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>259000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>285000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>259000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>246000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>217000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>265000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>215000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>182000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>118000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>145000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>129000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>99000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>74000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>89000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>19000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-199000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-721000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>109000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-598000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>99000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>79000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>99000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>129000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>106000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>113000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-15000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>121000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>98000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>50000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-19000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2475,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1118000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1218000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1145000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1098000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1148000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1136000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1047000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>944000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1082000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>919000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>970000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>520000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>611000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>562000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>443000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>312000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>382000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-73000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3428000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7368000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>343000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-11373000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>494000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>430000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>549000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>658000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>441000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>530000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2195000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>556000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-81000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>284000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-195000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>190000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1095000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1186000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1112000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1068000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1112000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1123000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1033000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>934000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1064000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>907000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>959000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>510000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>601000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>550000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>431000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>299000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>374000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-82000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3434000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7376000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>333000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-11383000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>492000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>421000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>539000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>644000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>430000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>525000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2178000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>545000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-74000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>279000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-205000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2787,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2855,8 +2915,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>24</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>24</v>
@@ -2873,11 +2933,11 @@
       <c r="AD29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-76000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>24</v>
@@ -2885,14 +2945,17 @@
       <c r="AH29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
+      <c r="AI29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2995,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3099,216 +3165,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E32" s="3">
         <v>44000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>47000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>46000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>54000</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="3">
         <v>39000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-91000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-75000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-95000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-24000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-29000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-16000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-19000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-69000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-22000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>59000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>29000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-30000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-31000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-48000</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-28000</v>
       </c>
       <c r="AE32" s="3">
         <v>-28000</v>
       </c>
       <c r="AF32" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-73000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-92000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-70000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>73000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-31000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1095000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1186000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1112000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1068000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1112000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1123000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1033000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>934000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1064000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>907000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>959000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>510000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>601000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>550000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>431000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>299000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>374000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-82000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3434000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7376000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>333000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-11383000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>492000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>421000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>539000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>644000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>430000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>525000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>545000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-74000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>279000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-205000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3411,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1095000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1186000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1112000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1068000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1112000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1123000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1033000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>934000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1064000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>907000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>959000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>510000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>601000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>550000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>431000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>299000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>374000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-82000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3434000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7376000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>333000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-11383000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>492000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>421000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>539000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>644000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>430000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>525000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>545000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-74000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>279000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-205000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3662,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3700,944 +3785,972 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3544000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3086000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2953000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2788000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2900000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2488000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1930000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1501000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1655000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2180000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1893000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1600000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1757000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1569000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1439000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1268000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>844000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1219000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1462000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1375000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1137000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1183000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1466000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1230000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1433000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1493000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1461000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1865000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1799000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1690000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1903000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1902000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2929000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3441000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1162000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1387000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1050000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>703000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1089000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1247000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1264000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1003000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1239000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1429000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>923000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1049000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1382000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1373000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1243000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1642000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2162000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2618000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2127000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1969000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1030000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1109000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>882000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>925000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1344000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1361000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1588000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2300000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>3290000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>3262000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>4315000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>5451000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>6328000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>7315000</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8011000</v>
+      </c>
+      <c r="E43" s="3">
         <v>8260000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8605000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8222000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7812000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8049000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7675000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7578000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7032000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6650000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6247000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5713000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5315000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5349000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5347000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5269000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5247000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5552000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5808000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7486000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7747000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8332000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8471000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8171000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7881000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8409000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8606000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8472000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>8084000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>9436000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8925000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>8636000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>9387000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>9565000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4375000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4573000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4504000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4549000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4387000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4305000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4360000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4286000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3999000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4143000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3968000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3719000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3272000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3296000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3267000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3303000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3354000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3542000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3601000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4148000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4130000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4341000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4389000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4224000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4010000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4108000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4120000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4174000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4046000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4308000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4338000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4288000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4225000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4572000</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1478000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1495000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1405000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1438000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1530000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>949000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>925000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1032000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1078000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1209000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1285000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1172000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>928000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>800000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>781000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1325000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1312000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1284000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1381000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1288000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1486000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1186000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1125000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1223000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1063000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1112000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1125000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1244000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1278000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1218000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1792000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1606000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1058000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1532000</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18570000</v>
+      </c>
+      <c r="E46" s="3">
         <v>18801000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18517000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17700000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17718000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17038000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16154000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15400000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15003000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15611000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14316000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13253000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12654000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12387000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12077000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12807000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12919000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>14215000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>14379000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>16266000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15530000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>16151000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>16333000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>15773000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>15731000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16483000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16900000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>18055000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>18497000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>19914000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>21273000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>21883000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>23927000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>26425000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3718000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1783000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1690000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1623000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3735000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1634000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1612000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1561000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1581000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1762000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1767000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1955000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2044000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2110000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2035000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2090000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2061000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1436000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1484000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1515000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1565000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1335000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1558000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1544000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1538000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1497000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1487000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1483000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1519000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1566000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1720000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1637000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8061000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7360000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7335000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7253000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7958000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6875000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6804000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6691000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6607000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6407000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6386000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6354000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6429000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6375000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6473000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6620000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6826000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7396000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7729000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8550000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9270000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>9605000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11359000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11533000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11679000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11739000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11504000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11556000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>11576000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>12338000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12358000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12507000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12821000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>13004000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17801000</v>
+      </c>
+      <c r="E49" s="3">
         <v>17681000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17728000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17253000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17474000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>16023000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16085000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16134000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15974000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16033000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16111000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16136000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16201000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16255000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16298000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>16375000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>16435000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>16541000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>16576000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>16597000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>23131000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>23394000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>33435000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>33556000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>33658000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>34064000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>34213000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>34337000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>34472000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>34653000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>34694000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>34788000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>34845000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>34794000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4740,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4844,112 +4960,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>785000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4150000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4103000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4027000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1072000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4243000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4171000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4069000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3970000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4280000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4247000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4269000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4183000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3911000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4025000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4144000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4193000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4478000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4499000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5666000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6816000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7505000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7906000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7915000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7901000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6263000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6052000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6047000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5923000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5183000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4971000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5277000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>4882000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>4734000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5052,112 +5174,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>48935000</v>
+      </c>
+      <c r="E54" s="3">
         <v>49775000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>49373000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>47856000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>47957000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>45813000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44826000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>43855000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>43135000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>44093000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>42827000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>41967000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>41511000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>41038000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>40908000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>42036000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>42434000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>44066000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>44667000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>48594000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>56312000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>57990000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>70591000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>70321000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>70507000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>70046000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>70156000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>71478000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>71987000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>73569000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>74862000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>76175000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>77956000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>80594000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5194,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5232,632 +5361,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4230000</v>
+      </c>
+      <c r="E57" s="3">
         <v>8346000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8082000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8040000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4613000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7922000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7638000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7497000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9121000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9034000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8528000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8638000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8382000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7615000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7635000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7956000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8442000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9201000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9824000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10168000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10663000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10364000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9851000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9702000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10223000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9419000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9367000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9598000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10036000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9676000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9413000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9380000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9939000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9378000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1237000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1059000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1050000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1441000</v>
       </c>
-      <c r="G58" s="3">
-        <v>1331000</v>
-      </c>
       <c r="H58" s="3">
+        <v>1123000</v>
+      </c>
+      <c r="I58" s="3">
         <v>1998000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1993000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2140000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1632000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>899000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>901000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>923000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>909000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1025000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>36000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>749000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>850000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1292000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>603000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1233000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>524000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>340000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>98000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>99000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1407000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3215000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3736000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4586000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3324000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1289000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2224000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2449000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3153000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3739000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5869000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3294000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3277000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3398000</v>
       </c>
-      <c r="G59" s="3">
-        <v>5826000</v>
-      </c>
       <c r="H59" s="3">
+        <v>6034000</v>
+      </c>
+      <c r="I59" s="3">
         <v>2608000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2532000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2615000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1265000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1201000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1154000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1135000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1068000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1095000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1113000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1168000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1199000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1158000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1238000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1861000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1911000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1779000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1824000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1896000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1856000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1966000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1963000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2011000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1922000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2049000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1890000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1947000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1967000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1855000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12811000</v>
+      </c>
+      <c r="E60" s="3">
         <v>12699000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12409000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12879000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13395000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12528000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12163000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12252000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12018000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11134000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10583000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10696000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10359000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9735000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8784000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9873000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10491000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11651000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11665000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>13262000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>13098000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12483000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11773000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11697000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>13486000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>14600000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>15066000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>16195000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>15282000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>13014000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>13527000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>13776000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>15059000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>14972000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11762000</v>
+      </c>
+      <c r="E61" s="3">
         <v>11928000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12314000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10838000</v>
       </c>
-      <c r="G61" s="3">
-        <v>11511000</v>
-      </c>
       <c r="H61" s="3">
+        <v>10909000</v>
+      </c>
+      <c r="I61" s="3">
         <v>11388000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11497000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10981000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10594000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12452000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12946000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13163000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13286000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>14370000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>15687000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>15834000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>16036000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>16471000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>16763000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>15409000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>14770000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>16333000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>16978000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>16449000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>14644000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>14159000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>13865000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>13526000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>14875000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>15871000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>16600000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>16538000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>16463000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>17538000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1433000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2073000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2060000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1924000</v>
       </c>
-      <c r="G62" s="3">
-        <v>1377000</v>
-      </c>
       <c r="H62" s="3">
+        <v>1979000</v>
+      </c>
+      <c r="I62" s="3">
         <v>1867000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1882000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1880000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2534000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2996000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2673000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2469000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2580000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3268000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3378000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3357000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3418000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3575000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3783000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3940000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4268000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4847000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5567000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>5651000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5791000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4339000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4328000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4431000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4569000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4674000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4783000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4807000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4905000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>5510000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5960,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6064,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6168,112 +6322,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>26585000</v>
+      </c>
+      <c r="E66" s="3">
         <v>27047000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>27093000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25933000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>26598000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>26106000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25892000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25475000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25450000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>26894000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26502000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26620000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>26507000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>27676000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28146000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>29493000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>30363000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>32125000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>32627000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>33033000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>32552000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>34077000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>34739000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>34218000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>34345000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>33513000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>33672000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>34554000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>35145000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>33996000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>35342000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>35569000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>36878000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>38360000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6310,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6414,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6518,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6622,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6726,112 +6896,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16395000</v>
+      </c>
+      <c r="E72" s="3">
         <v>15687000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>14890000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14172000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13497000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12742000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11974000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11296000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10719000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9904000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9244000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8532000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8199000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7775000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7399000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7142000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7018000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6818000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7073000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>10681000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>18751000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>19111000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>31186000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>31386000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>31658000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>31712000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>31760000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>32022000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>32190000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>35136000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>35284000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>36052000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>36470000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>37370000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6934,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7038,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7142,112 +7324,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21130000</v>
+      </c>
+      <c r="E76" s="3">
         <v>21511000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21071000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20736000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20189000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19386000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18608000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18068000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17685000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17199000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16325000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15347000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15004000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13362000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12762000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12543000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12071000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11941000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12040000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15561000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>23760000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>23913000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>35852000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>36103000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>36162000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>36533000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>36484000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>36924000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>36842000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>39573000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>39520000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>40606000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>41078000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>42234000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7350,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1095000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1186000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1112000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1068000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1112000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1123000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1033000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>934000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1064000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>907000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>959000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>510000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>601000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>550000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>431000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>299000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>374000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-82000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3434000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7376000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>333000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-11383000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>492000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>421000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>539000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>644000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>430000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>525000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>545000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-74000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>279000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-205000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7601,112 +7798,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E83" s="3">
         <v>501000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>484000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>487000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>71000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>457000</v>
       </c>
       <c r="I83" s="3">
         <v>457000</v>
       </c>
       <c r="J83" s="3">
+        <v>457000</v>
+      </c>
+      <c r="K83" s="3">
         <v>458000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>549000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>533000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>532000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>533000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>532000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>530000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>526000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>532000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>583000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>587000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>604000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>792000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>848000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>900000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>938000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>903000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>919000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>887000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>876000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>874000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>906000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>956000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>986000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>989000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1016000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>998000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7809,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7913,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8017,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8121,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8225,112 +8438,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2390000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2449000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1436000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>327000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3022000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1677000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1608000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>330000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1614000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1567000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>408000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>131000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1932000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1070000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1220000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>429000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>878000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>479000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>803000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>784000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2252000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1745000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1108000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>326000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2331000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1827000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>987000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>568000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2251000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1898000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>858000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>656000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2013000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1406000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8367,112 +8586,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-702000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-594000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-598000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-520000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-710000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-602000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-591000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-543000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-572000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-382000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-360000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-304000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-447000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-273000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-243000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-178000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-258000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-251000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-407000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-494000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-413000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-404000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-413000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-621000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-565000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-520000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-454000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-625000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-598000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-503000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-381000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-654000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-403000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8575,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8679,112 +8905,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-477000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1024000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1493000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-151000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-520000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-733000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-983000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-547000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-272000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1083000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>82000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-115000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-526000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-619000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>15000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>211000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>246000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-740000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-547000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1312000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-203000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-934000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-644000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-230000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-315000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-895000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-112000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>282000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>221000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>473000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-55000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-32000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8821,22 +9053,23 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>389000</v>
+      </c>
+      <c r="E96" s="3">
         <v>393000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>394000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>357000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>356000</v>
       </c>
       <c r="H96" s="3">
         <v>356000</v>
@@ -8845,19 +9078,19 @@
         <v>356000</v>
       </c>
       <c r="J96" s="3">
+        <v>356000</v>
+      </c>
+      <c r="K96" s="3">
         <v>249000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-248000</v>
       </c>
       <c r="L96" s="3">
         <v>-248000</v>
       </c>
       <c r="M96" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="N96" s="3">
         <v>-177000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-175000</v>
       </c>
       <c r="O96" s="3">
         <v>-175000</v>
@@ -8869,7 +9102,7 @@
         <v>-175000</v>
       </c>
       <c r="R96" s="3">
-        <v>-174000</v>
+        <v>-175000</v>
       </c>
       <c r="S96" s="3">
         <v>-174000</v>
@@ -8878,10 +9111,10 @@
         <v>-174000</v>
       </c>
       <c r="U96" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-694000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-692000</v>
       </c>
       <c r="W96" s="3">
         <v>-692000</v>
@@ -8890,34 +9123,34 @@
         <v>-692000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-693000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-692000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-692000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-693000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-692000</v>
       </c>
       <c r="AE96" s="3">
         <v>-692000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-697000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-696000</v>
       </c>
       <c r="AI96" s="3">
         <v>-696000</v>
@@ -8925,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>-696000</v>
       </c>
+      <c r="AK96" s="3">
+        <v>-696000</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9029,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9133,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9237,316 +9479,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1431000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1295000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>221000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-267000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2009000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-382000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-183000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>62000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1844000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-180000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-188000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-170000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1220000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-322000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1070000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-212000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1504000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>21000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-167000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>777000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2097000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1090000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-234000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-297000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2069000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-900000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1264000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-787000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>278000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2342000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1332000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1637000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2389000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1116000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-13000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-23000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-17000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-23000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-17000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>6000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>5000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-11000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>6000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>3000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>10000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>9000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-104000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>458000</v>
+      </c>
+      <c r="E102" s="3">
         <v>133000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>165000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-112000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>412000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>558000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>429000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-154000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-525000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>287000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>293000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-157000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>188000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>130000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>171000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>424000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-375000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-243000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>87000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>238000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-46000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-283000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>236000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-203000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-60000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>32000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-404000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>66000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>109000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-213000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1027000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-512000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>494000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
@@ -656,480 +656,493 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8490000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9284000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9159000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9139000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8707000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8990000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8310000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8099000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7736000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7878000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7477000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6773000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5962000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6225000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5847000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5634000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5223000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5532000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5258000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5356000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7455000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8228000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8541000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8269000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7879000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8179000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8504000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8303000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7829000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8179000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>7905000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7462000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6894000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7107000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7019000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6884000</v>
+      </c>
+      <c r="E9" s="3">
         <v>7323000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7237000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7247000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6993000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7093000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6592000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6502000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6285000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6307000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6042000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5568000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5013000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5136000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4862000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4768000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4504000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4828000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4624000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4925000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>6614000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7136000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7382000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7236000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6956000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>7193000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>7305000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>7184000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6834000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>7169000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>6787000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>6469000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6082000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>6113000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>6114000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1606000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1961000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1922000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1892000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1714000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1897000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1718000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1597000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1451000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1571000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1435000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1205000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>949000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1089000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>985000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>866000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>719000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>704000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>634000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>431000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>841000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1092000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1159000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1033000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>923000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>986000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1199000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1119000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>995000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1010000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1118000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>993000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>812000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>994000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>905000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,115 +1180,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>172000</v>
+      </c>
+      <c r="E12" s="3">
         <v>192000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>187000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>188000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>182000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>187000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>186000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>163000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>174000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>178000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>160000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>154000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>141000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>145000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>140000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>134000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>135000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>128000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>137000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>142000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>173000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>190000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>176000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>179000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>173000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>178000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>177000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>175000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>172000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>192000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>189000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>196000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>211000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>262000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1381,53 +1398,56 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>206000</v>
+      </c>
+      <c r="E14" s="3">
         <v>262000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>98000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>142000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>25000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>146000</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="3">
         <v>-36000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-83000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-216000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-26000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-28000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1435,91 +1455,94 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-42000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>350000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>3724000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>8523000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>209000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>12692000</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-43000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>184000</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>2796000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>49000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>591000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>82000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>676000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>237000</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>640000</v>
+      </c>
+      <c r="E15" s="3">
         <v>14000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>640000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>631000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>600000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>56000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>579000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>561000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>563000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1595,8 +1618,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1657,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7152000</v>
+      </c>
+      <c r="E17" s="3">
         <v>7595000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7514000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7529000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7296000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7376000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6859000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6761000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6550000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6501000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6296000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5592000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5225000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5361000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5082000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4972000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4720000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4986000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5196000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8872000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15437000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7664000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>20370000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7529000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7241000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7442000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7587000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7657000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7117000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10266000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7140000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7366000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6473000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>7149000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>6696000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1338000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1689000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1645000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1610000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1411000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1614000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1451000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1338000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1186000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1377000</v>
-      </c>
-      <c r="M18" s="3">
-        <v>1181000</v>
       </c>
       <c r="N18" s="3">
         <v>1181000</v>
       </c>
       <c r="O18" s="3">
+        <v>1181000</v>
+      </c>
+      <c r="P18" s="3">
         <v>737000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>864000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>765000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>662000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>503000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>546000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>62000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3516000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-7982000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>564000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-11829000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>740000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>638000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>737000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>917000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>646000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>712000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2087000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>765000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>96000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>421000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-42000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>323000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1884,543 +1917,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-46000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-44000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-47000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-46000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-54000</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3">
         <v>-39000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>91000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>75000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>95000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>24000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>29000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>56000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>16000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>19000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>69000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>22000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-59000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-29000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>30000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>20000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>31000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>34000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>16000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>41000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>48000</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>28000</v>
       </c>
       <c r="AF20" s="3">
         <v>28000</v>
       </c>
       <c r="AG20" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AH20" s="3">
         <v>73000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>92000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>70000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-73000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>2020000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1749000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2329000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2288000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2057000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1724000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2030000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1899000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1788000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2017000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1789000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1808000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1294000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1425000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1351000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1204000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1054000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1198000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>671000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2971000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-7219000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1442000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-10909000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1709000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1575000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1672000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1845000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1570000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1614000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-1153000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1794000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1174000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1480000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>901000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1352000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E22" s="3">
         <v>131000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>136000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>132000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>113000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>130000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>129000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>127000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>117000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>121000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>122000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>124000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>123000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>137000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>130000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>136000</v>
       </c>
       <c r="S22" s="3">
         <v>136000</v>
       </c>
       <c r="T22" s="3">
+        <v>136000</v>
+      </c>
+      <c r="U22" s="3">
         <v>144000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>138000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>52000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>78000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>142000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>162000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>178000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>163000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>105000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>171000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>147000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>97000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>151000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>161000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>171000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>157000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>99000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1063000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1387000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1507000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1421000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1357000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1433000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1395000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1293000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1161000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1347000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1134000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1152000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>638000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>756000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>691000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>542000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>386000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>471000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-54000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3627000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8089000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>452000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-11971000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>593000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>509000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>648000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>787000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>547000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>643000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2210000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>677000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>17000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>334000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-214000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>200000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>234000</v>
+      </c>
+      <c r="E24" s="3">
         <v>269000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>289000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>276000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>259000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>285000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>259000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>246000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>217000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>265000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>215000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>182000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>118000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>145000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>129000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>99000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>74000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>89000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>19000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-199000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-721000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>109000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-598000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>99000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>79000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>99000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>129000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>106000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>113000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-15000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>121000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>98000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>50000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-19000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2526,222 +2575,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>829000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1118000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1218000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1145000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1098000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1148000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1136000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1047000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>944000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1082000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>919000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>970000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>520000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>611000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>562000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>443000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>312000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>382000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-73000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3428000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7368000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>343000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-11373000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>494000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>430000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>549000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>658000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>441000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>530000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2195000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>556000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-81000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>284000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-195000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>190000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>797000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1095000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1186000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1112000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1068000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1112000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1123000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1033000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>934000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1064000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>907000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>959000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>510000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>601000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>550000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>431000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>299000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>374000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-82000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3434000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7376000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>333000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-11383000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>492000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>421000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>539000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>644000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>430000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>525000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2178000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>545000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-74000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>279000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-205000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2847,8 +2905,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2918,8 +2979,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>24</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>24</v>
@@ -2936,11 +2997,11 @@
       <c r="AE29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-76000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>24</v>
@@ -2948,14 +3009,17 @@
       <c r="AI29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK29" s="3" t="s">
+      <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3125,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,222 +3235,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E32" s="3">
         <v>46000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>44000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>47000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>46000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>54000</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="3">
         <v>39000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-91000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-75000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-95000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-24000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-29000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-56000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-16000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-19000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-69000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-22000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>59000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>29000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-30000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-48000</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-28000</v>
       </c>
       <c r="AF32" s="3">
         <v>-28000</v>
       </c>
       <c r="AG32" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-73000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-92000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-70000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>73000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-31000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>797000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1095000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1186000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1112000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1068000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1112000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1123000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1033000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>934000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1064000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>907000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>959000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>510000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>601000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>550000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>431000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>299000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>374000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-82000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3434000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7376000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>333000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-11383000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>492000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>421000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>539000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>644000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>430000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>525000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>545000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-74000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>279000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-205000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3565,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>797000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1095000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1186000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1112000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1068000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1112000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1123000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1033000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>934000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1064000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>907000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>959000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>510000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>601000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>550000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>431000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>299000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>374000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-82000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3434000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7376000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>333000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-11383000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>492000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>421000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>539000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>644000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>430000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>525000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>545000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-74000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>279000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-205000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3832,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,971 +3872,999 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2936000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3544000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3086000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2953000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2788000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2900000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2488000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1930000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1501000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1655000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2180000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1893000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1600000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1757000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1569000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1439000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1268000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>844000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1219000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1462000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1375000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1137000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1183000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1466000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1230000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1433000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1493000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1461000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1865000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1799000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1690000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1903000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1902000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2929000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3441000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>999000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1162000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1387000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1050000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>703000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1089000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1247000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1264000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1003000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1239000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1429000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>923000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1049000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1382000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1373000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1243000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1642000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2162000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2618000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2127000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1969000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1030000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1109000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>882000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>925000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1344000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1361000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1588000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2300000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>3290000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>3262000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>4315000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>5451000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>6328000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>7315000</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8604000</v>
+      </c>
+      <c r="E43" s="3">
         <v>8011000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8260000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8605000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8222000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7812000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8049000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7675000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7578000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7032000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6650000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6247000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5713000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5315000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5349000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5347000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5269000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5247000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5552000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5808000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7486000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7747000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8332000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8471000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8171000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7881000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8409000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8606000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>8472000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>8084000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>9436000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>8925000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>8636000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>9387000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>9565000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4650000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4375000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4573000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4504000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4549000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4387000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4305000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4360000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4286000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3999000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4143000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3968000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3719000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3272000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3296000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3267000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3303000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3354000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3542000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3601000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4148000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4130000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4341000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4389000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4224000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4010000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4108000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4120000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4174000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4046000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4308000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4338000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4288000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4225000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4572000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1406000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1478000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1495000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1405000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1438000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1530000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>949000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>925000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1032000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1078000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1209000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1285000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1172000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>928000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>800000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>781000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1325000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1312000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1284000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1381000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1288000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1486000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1186000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1125000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1223000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1063000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1112000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1125000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1244000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1278000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1218000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1792000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1606000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1058000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1532000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18595000</v>
+      </c>
+      <c r="E46" s="3">
         <v>18570000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18801000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18517000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17700000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17718000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17038000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16154000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15400000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15003000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15611000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14316000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13253000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12654000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12387000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12077000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12807000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12919000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>14215000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>14379000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>16266000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>15530000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>16151000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16333000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>15773000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>15731000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16483000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>16900000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>18055000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>18497000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>19914000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>21273000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>21883000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>23927000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>26425000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1644000</v>
+      </c>
+      <c r="E47" s="3">
         <v>3718000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1783000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1690000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1623000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3735000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1634000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1612000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1561000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1581000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1762000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1767000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1955000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2044000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2110000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2035000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2090000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2061000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1436000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1484000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1515000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1565000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1335000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1558000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1544000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1538000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1497000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1487000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1483000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1519000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1566000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1720000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1637000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7399000</v>
+      </c>
+      <c r="E48" s="3">
         <v>8061000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7360000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7335000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7253000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7958000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6875000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6804000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6691000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6607000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6407000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6386000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6354000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6429000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6375000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6473000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6620000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6826000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7396000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7729000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8550000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>9270000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9605000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11359000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11533000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11679000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11739000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11504000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>11556000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>11576000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>12338000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12358000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12507000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12821000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>13004000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17600000</v>
+      </c>
+      <c r="E49" s="3">
         <v>17801000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17681000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17728000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17253000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17474000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16023000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16085000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16134000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15974000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16033000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16111000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16136000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16201000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16255000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>16298000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>16375000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>16435000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>16541000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>16576000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>16597000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>23131000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>23394000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>33435000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>33556000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>33658000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>34064000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>34213000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>34337000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>34472000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>34653000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>34694000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>34788000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>34845000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>34794000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4970,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,115 +5080,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3764000</v>
+      </c>
+      <c r="E52" s="3">
         <v>785000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4150000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4103000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4027000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1072000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4243000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4171000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4069000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3970000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4280000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4247000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4269000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4183000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3911000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4025000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4144000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4193000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4478000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4499000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5666000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6816000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7505000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7906000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7915000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7901000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6263000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6052000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6047000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5923000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5183000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>4971000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5277000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>4882000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>4734000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5300,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>49002000</v>
+      </c>
+      <c r="E54" s="3">
         <v>48935000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>49775000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>49373000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>47856000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>47957000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>45813000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>44826000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>43855000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>43135000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>44093000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>42827000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>41967000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>41511000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>41038000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>40908000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>42036000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>42434000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>44066000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>44667000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>48594000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>56312000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>57990000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>70591000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>70321000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>70507000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>70046000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>70156000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>71478000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>71987000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>73569000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>74862000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>76175000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>77956000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>80594000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5452,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,650 +5492,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8121000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4230000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8346000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8082000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8040000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4613000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7922000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7638000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7497000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9121000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9034000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8528000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8638000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8382000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7615000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7635000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7956000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8442000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9201000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9824000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10168000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10663000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10364000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9851000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9702000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10223000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9419000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9367000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9598000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10036000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9676000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9413000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9380000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9939000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>9378000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3475000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1237000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1059000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1050000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1441000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1123000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1998000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1993000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2140000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1632000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>899000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>901000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>923000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>909000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1025000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>36000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>749000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>850000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1292000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>603000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1233000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>524000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>340000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>98000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>99000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1407000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3215000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3736000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4586000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3324000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1289000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2224000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2449000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3153000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3739000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3440000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5869000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3294000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3277000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3398000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6034000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2608000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2532000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2615000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1265000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1201000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1154000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1135000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1068000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1095000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1113000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1168000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1199000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1158000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1238000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1861000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1911000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1779000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1824000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1896000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1856000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1966000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1963000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2011000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1922000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2049000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1890000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1947000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1967000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1855000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15036000</v>
+      </c>
+      <c r="E60" s="3">
         <v>12811000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12699000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12409000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12879000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13395000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12528000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12163000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12252000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12018000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11134000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10583000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10696000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10359000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9735000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8784000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9873000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10491000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11651000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11665000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>13262000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>13098000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>12483000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11773000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>11697000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>13486000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>14600000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>15066000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>16195000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>15282000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>13014000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>13527000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>13776000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>15059000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>14972000</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10663000</v>
+      </c>
+      <c r="E61" s="3">
         <v>11762000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11928000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12314000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10838000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10909000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11388000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11497000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10981000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10594000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12452000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12946000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13163000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13286000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14370000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>15687000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>15834000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>16036000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>16471000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>16763000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>15409000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14770000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>16333000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>16978000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>16449000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>14644000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>14159000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>13865000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>13526000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>14875000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>15871000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>16600000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>16538000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>16463000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>17538000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2011000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1433000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2073000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2060000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1924000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1979000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1867000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1882000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1880000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2534000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2996000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2673000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2469000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2580000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3268000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3378000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3357000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3418000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3575000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3783000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3940000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4268000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4847000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>5567000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5651000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5791000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4339000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4328000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4431000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4569000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4674000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4783000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4807000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4905000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>5510000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6260,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6218,8 +6370,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6480,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>28254000</v>
+      </c>
+      <c r="E66" s="3">
         <v>26585000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>27047000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>27093000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25933000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>26598000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>26106000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25892000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25475000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25450000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26894000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26502000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>26620000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>26507000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>27676000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>28146000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>29493000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>30363000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>32125000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>32627000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>33033000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>32552000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>34077000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>34739000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>34218000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>34345000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>33513000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>33672000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>34554000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>35145000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>33996000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>35342000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>35569000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>36878000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>38360000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6632,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6740,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6850,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6960,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7070,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16804000</v>
+      </c>
+      <c r="E72" s="3">
         <v>16395000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15687000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14890000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14172000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>13497000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12742000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11974000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11296000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10719000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9904000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9244000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8532000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8199000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7775000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7399000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7142000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7018000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6818000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7073000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>10681000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>18751000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>19111000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>31186000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>31386000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>31658000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>31712000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>31760000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>32022000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>32190000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>35136000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>35284000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>36052000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>36470000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>37370000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7290,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7400,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7510,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19515000</v>
+      </c>
+      <c r="E76" s="3">
         <v>21130000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21511000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21071000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20736000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20189000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19386000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18608000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18068000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17685000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17199000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16325000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15347000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15004000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13362000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12762000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12543000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12071000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11941000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12040000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15561000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>23760000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>23913000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>35852000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>36103000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>36162000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>36533000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>36484000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>36924000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>36842000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>39573000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>39520000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>40606000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>41078000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>42234000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7730,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>797000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1095000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1186000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1112000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1068000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1112000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1123000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1033000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>934000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1064000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>907000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>959000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>510000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>601000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>550000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>431000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>299000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>374000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-82000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3434000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7376000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>333000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-11383000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>492000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>421000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>539000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>644000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>430000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>525000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>545000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-74000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>279000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-205000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,115 +7997,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>519000</v>
+      </c>
+      <c r="E83" s="3">
         <v>56000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>501000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>484000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>487000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>71000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>457000</v>
       </c>
       <c r="J83" s="3">
         <v>457000</v>
       </c>
       <c r="K83" s="3">
+        <v>457000</v>
+      </c>
+      <c r="L83" s="3">
         <v>458000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>549000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>533000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>532000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>533000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>532000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>530000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>526000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>532000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>583000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>587000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>604000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>792000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>848000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>900000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>938000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>903000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>919000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>887000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>876000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>874000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>906000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>956000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>986000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>989000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1016000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>998000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8215,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8325,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8435,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8545,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8655,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>660000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2390000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2449000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1436000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>327000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3022000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1677000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1608000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>330000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1614000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1567000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>408000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>131000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1932000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1070000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1220000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>429000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>878000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>479000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>803000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>784000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2252000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1745000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1108000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>326000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2331000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1827000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>987000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>568000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2251000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1898000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>858000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>656000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2013000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1406000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,115 +8807,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-506000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-702000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-594000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-598000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-520000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-710000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-602000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-591000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-543000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-572000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-382000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-360000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-304000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-447000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-273000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-243000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-178000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-258000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-251000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-407000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-494000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-413000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-404000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-413000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-621000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-565000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-520000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-454000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-625000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-598000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-503000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-381000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-654000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-403000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9025,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,115 +9135,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-432000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-477000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1024000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1493000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-151000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-520000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-733000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-983000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-547000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-272000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1083000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>82000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-115000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-526000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-619000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>15000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>211000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>246000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-740000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-547000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1312000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-203000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-934000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-644000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-230000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-315000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-895000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-112000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>282000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>221000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>473000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-55000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-32000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,25 +9287,26 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>386000</v>
+      </c>
+      <c r="E96" s="3">
         <v>389000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>393000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>394000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>357000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>356000</v>
       </c>
       <c r="I96" s="3">
         <v>356000</v>
@@ -9081,19 +9315,19 @@
         <v>356000</v>
       </c>
       <c r="K96" s="3">
+        <v>356000</v>
+      </c>
+      <c r="L96" s="3">
         <v>249000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-248000</v>
       </c>
       <c r="M96" s="3">
         <v>-248000</v>
       </c>
       <c r="N96" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-177000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-175000</v>
       </c>
       <c r="P96" s="3">
         <v>-175000</v>
@@ -9105,7 +9339,7 @@
         <v>-175000</v>
       </c>
       <c r="S96" s="3">
-        <v>-174000</v>
+        <v>-175000</v>
       </c>
       <c r="T96" s="3">
         <v>-174000</v>
@@ -9114,10 +9348,10 @@
         <v>-174000</v>
       </c>
       <c r="V96" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="W96" s="3">
         <v>-694000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-692000</v>
       </c>
       <c r="X96" s="3">
         <v>-692000</v>
@@ -9126,34 +9360,34 @@
         <v>-692000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-692000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-692000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-693000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-692000</v>
       </c>
       <c r="AF96" s="3">
         <v>-692000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-697000</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-696000</v>
       </c>
       <c r="AJ96" s="3">
         <v>-696000</v>
@@ -9161,8 +9395,11 @@
       <c r="AK96" s="3">
         <v>-696000</v>
       </c>
+      <c r="AL96" s="3">
+        <v>-696000</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9505,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9615,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,325 +9725,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-878000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1431000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1295000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>221000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-267000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2009000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-382000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-183000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>62000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1844000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-180000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-188000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-170000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1220000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-322000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1070000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-212000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1504000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>21000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-167000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>777000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2097000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1090000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-234000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-297000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2069000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-900000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1264000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-787000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>278000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2342000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1332000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1637000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2389000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1116000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-81000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-13000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-23000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-17000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-23000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-17000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>6000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-4000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>5000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-11000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>6000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>3000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>10000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-104000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-608000</v>
+      </c>
+      <c r="E102" s="3">
         <v>458000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>133000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>165000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-112000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>412000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>558000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>429000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-154000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-525000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>287000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>293000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-157000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>188000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>130000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>171000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>424000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-375000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-243000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>87000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>238000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-46000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-283000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>236000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-203000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-60000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>32000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-404000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>66000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>109000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-213000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1027000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-512000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>494000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>SLB</t>
   </si>
@@ -656,493 +656,506 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8546000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8490000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9284000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9159000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9139000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8707000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8990000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8310000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8099000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7736000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7878000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7477000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6773000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5962000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6225000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5847000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5634000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5223000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5532000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5258000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5356000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7455000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8228000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8541000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8269000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7879000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8179000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8504000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8303000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7829000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8179000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7905000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7462000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>6894000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7107000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>7019000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6934000</v>
+      </c>
+      <c r="E9" s="3">
         <v>6884000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7323000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7237000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7247000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6993000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7093000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6592000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6502000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6285000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6307000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6042000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5568000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5013000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5136000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4862000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4768000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4504000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4828000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4624000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4925000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6614000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7136000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7382000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7236000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6956000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>7193000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>7305000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7184000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>6834000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>7169000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>6787000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6469000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>6082000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>6113000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>6114000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1612000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1606000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1961000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1922000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1892000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1714000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1897000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1718000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1597000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1451000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1571000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1435000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1205000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>949000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1089000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>985000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>866000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>719000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>704000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>634000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>431000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>841000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1092000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1159000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1033000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>923000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>986000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1199000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1119000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>995000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1010000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1118000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>993000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>812000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>994000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>905000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,118 +1194,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E12" s="3">
         <v>172000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>192000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>187000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>188000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>182000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>187000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>186000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>163000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>174000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>178000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>160000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>154000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>141000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>145000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>140000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>134000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>135000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>128000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>137000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>142000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>173000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>190000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>176000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>179000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>173000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>178000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>177000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>175000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>172000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>192000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>189000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>196000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>211000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>262000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1401,56 +1418,59 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E14" s="3">
         <v>206000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>262000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>98000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>142000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>25000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>146000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" s="3">
         <v>-36000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-83000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-216000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-28000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
@@ -1458,94 +1478,97 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-42000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>350000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>3724000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>8523000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>209000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>12692000</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-43000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>184000</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>2796000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>49000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>591000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>82000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>676000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>237000</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>633000</v>
+      </c>
+      <c r="E15" s="3">
         <v>640000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>14000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>640000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>631000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>600000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>56000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>579000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>561000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>563000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1621,8 +1644,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1658,228 +1684,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7201000</v>
+      </c>
+      <c r="E17" s="3">
         <v>7152000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7595000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7514000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7529000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7296000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7376000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6859000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6761000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6550000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6501000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6296000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5592000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5225000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5361000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5082000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4972000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4720000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4986000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5196000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8872000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>15437000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7664000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>20370000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7529000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7241000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7442000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7587000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7657000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7117000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>10266000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7140000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>7366000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6473000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>7149000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>6696000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1345000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1338000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1689000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1645000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1610000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1411000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1614000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1451000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1338000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1186000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1377000</v>
-      </c>
-      <c r="N18" s="3">
-        <v>1181000</v>
       </c>
       <c r="O18" s="3">
         <v>1181000</v>
       </c>
       <c r="P18" s="3">
+        <v>1181000</v>
+      </c>
+      <c r="Q18" s="3">
         <v>737000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>864000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>765000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>662000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>503000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>546000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>62000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3516000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-7982000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>564000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-11829000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>740000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>638000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>737000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>917000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>646000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>712000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2087000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>765000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>96000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>421000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-42000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>323000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1918,558 +1951,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-72000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-42000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-46000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-44000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-47000</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="3">
         <v>-46000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-54000</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M20" s="3">
         <v>-39000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>91000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>75000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>95000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>24000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>29000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>56000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>16000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>19000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>69000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>22000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-59000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-29000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>30000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>20000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>31000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>34000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>16000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>41000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>48000</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>28000</v>
       </c>
       <c r="AG20" s="3">
         <v>28000</v>
       </c>
       <c r="AH20" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AI20" s="3">
         <v>73000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>92000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>70000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-73000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>2050000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2020000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1749000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2329000</v>
       </c>
-      <c r="G21" s="3">
-        <v>2288000</v>
-      </c>
       <c r="H21" s="3">
+        <v>2241000</v>
+      </c>
+      <c r="I21" s="3">
         <v>2057000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1724000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2030000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1899000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1788000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2017000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1789000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1808000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1294000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1425000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1351000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1204000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1054000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1198000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>671000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2971000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-7219000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1442000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-10909000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1709000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1575000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1672000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1845000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1570000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1614000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-1153000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1794000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1174000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1480000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>901000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1352000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E22" s="3">
         <v>147000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>131000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>136000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>132000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>113000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>130000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>129000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>127000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>117000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>121000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>122000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>124000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>123000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>137000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>130000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>136000</v>
       </c>
       <c r="T22" s="3">
         <v>136000</v>
       </c>
       <c r="U22" s="3">
+        <v>136000</v>
+      </c>
+      <c r="V22" s="3">
         <v>144000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>138000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>52000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>78000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>142000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>162000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>178000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>163000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>105000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>171000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>147000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>97000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>151000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>161000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>171000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>157000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>99000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1285000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1063000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1387000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1507000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1421000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1357000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1433000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1395000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1293000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1161000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1347000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1134000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1152000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>638000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>756000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>691000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>542000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>386000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>471000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-54000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3627000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8089000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>452000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-11971000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>593000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>509000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>648000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>787000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>547000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>643000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2210000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>677000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>17000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>334000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-214000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>200000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>237000</v>
+      </c>
+      <c r="E24" s="3">
         <v>234000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>269000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>289000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>276000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>259000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>285000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>259000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>246000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>217000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>265000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>215000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>182000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>118000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>145000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>129000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>99000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>74000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>89000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>19000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-199000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-721000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>109000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-598000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>99000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>79000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>99000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>129000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>106000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>113000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-15000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>121000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>98000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>50000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-19000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2578,228 +2627,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1048000</v>
+      </c>
+      <c r="E26" s="3">
         <v>829000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1118000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1218000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1145000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1098000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1148000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1136000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1047000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>944000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1082000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>919000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>970000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>520000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>611000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>562000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>443000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>312000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>382000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-73000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3428000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7368000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>343000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-11373000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>494000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>430000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>549000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>658000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>441000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>530000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2195000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>556000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-81000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>284000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-195000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>190000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1014000</v>
+      </c>
+      <c r="E27" s="3">
         <v>797000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1095000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1186000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1112000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1068000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1112000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1123000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1033000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>934000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1064000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>907000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>959000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>510000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>601000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>550000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>431000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>299000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>374000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-82000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3434000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7376000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>333000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-11383000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>492000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>421000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>539000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>644000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>430000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>525000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2178000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>545000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-74000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>279000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-205000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2908,8 +2966,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2982,8 +3043,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
@@ -3000,11 +3061,11 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-76000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>24</v>
@@ -3012,14 +3073,17 @@
       <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="3" t="s">
+      <c r="AK29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3128,8 +3192,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3238,228 +3305,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E32" s="3">
         <v>42000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>46000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>44000</v>
       </c>
-      <c r="G32" s="3">
-        <v>47000</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="3">
         <v>46000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>54000</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M32" s="3">
         <v>39000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-91000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-75000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-95000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-24000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-29000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-56000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-16000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-19000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-69000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-22000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>59000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>29000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-30000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-48000</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-28000</v>
       </c>
       <c r="AG32" s="3">
         <v>-28000</v>
       </c>
       <c r="AH32" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-73000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-92000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-70000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>73000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-31000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1014000</v>
+      </c>
+      <c r="E33" s="3">
         <v>797000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1095000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1186000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1112000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1068000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1112000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1123000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1033000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>934000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1064000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>907000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>959000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>510000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>601000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>550000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>431000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>299000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>374000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-82000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3434000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7376000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>333000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-11383000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>492000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>421000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>539000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>644000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>430000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>525000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>545000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-74000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>279000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-205000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3568,233 +3644,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1014000</v>
+      </c>
+      <c r="E35" s="3">
         <v>797000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1095000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1186000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1112000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1068000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1112000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1123000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1033000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>934000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1064000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>907000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>959000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>510000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>601000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>550000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>431000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>299000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>374000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-82000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3434000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7376000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>333000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-11383000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>492000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>421000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>539000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>644000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>430000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>525000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>545000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-74000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>279000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-205000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3833,8 +3918,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3873,778 +3959,800 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3236000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2936000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3544000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3086000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2953000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2788000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2900000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2488000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1930000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1501000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1655000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2180000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1893000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1600000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1757000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1569000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1439000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1268000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>844000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1219000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1462000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1375000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1137000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1183000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1466000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1230000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1433000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1493000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1461000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1865000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1799000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1690000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1903000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1902000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2929000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3441000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>511000</v>
+      </c>
+      <c r="E42" s="3">
         <v>999000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1162000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1387000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1050000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>703000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1089000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1247000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1264000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1003000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1239000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1429000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>923000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1049000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1382000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1373000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1243000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1642000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2162000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2618000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2127000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1969000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1030000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1109000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>882000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>925000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1344000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1361000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1588000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2300000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>3290000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>3262000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>4315000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>5451000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>6328000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>7315000</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8586000</v>
+      </c>
+      <c r="E43" s="3">
         <v>8604000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8011000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8260000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8605000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8222000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7812000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8049000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7675000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7578000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7032000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6650000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6247000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5713000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5315000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5349000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5347000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5269000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5247000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5552000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5808000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7486000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7747000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8332000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8471000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8171000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7881000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8409000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>8606000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>8472000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8084000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>9436000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>8925000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>8636000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>9387000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>9565000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4740000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4650000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4375000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4573000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4504000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4549000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4387000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4305000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4360000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4286000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3999000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4143000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3968000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3719000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3272000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3296000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3267000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3303000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3354000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3542000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3601000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4148000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4130000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4341000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4389000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4224000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4010000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4108000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4120000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4174000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4046000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4308000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4338000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4288000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4225000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>4572000</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1380000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1406000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1478000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1495000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1405000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1438000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1530000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>949000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>925000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1032000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1078000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1209000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1285000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1172000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>928000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>800000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>781000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1325000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1312000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1284000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1381000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1288000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1486000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1186000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1125000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1223000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1063000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1112000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1125000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1244000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1278000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1218000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1792000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1606000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1058000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1532000</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18453000</v>
+      </c>
+      <c r="E46" s="3">
         <v>18595000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18570000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18801000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18517000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17700000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>17718000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17038000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16154000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15400000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15003000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15611000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14316000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13253000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12654000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12387000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12077000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12807000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12919000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>14215000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>14379000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>16266000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>15530000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16151000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16333000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>15773000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>15731000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>16483000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>16900000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>18055000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>18497000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>19914000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>21273000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>21883000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>23927000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>26425000</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1888000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1644000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3718000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1783000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1690000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1623000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3735000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1634000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1612000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1561000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1581000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1762000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1767000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1955000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2044000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2110000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2035000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2090000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2061000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1436000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1484000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1515000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1565000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1335000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1558000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1544000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1538000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1497000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1487000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1483000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1519000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1566000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1720000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1637000</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4652,219 +4760,225 @@
         <v>7399000</v>
       </c>
       <c r="E48" s="3">
+        <v>7399000</v>
+      </c>
+      <c r="F48" s="3">
         <v>8061000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7360000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7335000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7253000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7958000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6875000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6804000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6691000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6607000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6407000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6386000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6354000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6429000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6375000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6473000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6620000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6826000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7396000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7729000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8550000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>9270000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9605000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11359000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11533000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11679000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11739000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>11504000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>11556000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>11576000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>12338000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12358000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12507000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12821000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>13004000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17551000</v>
+      </c>
+      <c r="E49" s="3">
         <v>17600000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17801000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17681000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17728000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17253000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>17474000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16023000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16085000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16134000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15974000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16033000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16111000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16136000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16201000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>16255000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>16298000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>16375000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>16435000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>16541000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>16576000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>16597000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>23131000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>23394000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>33435000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>33556000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>33658000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>34064000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>34213000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>34337000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>34472000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>34653000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>34694000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>34788000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>34845000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>34794000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4973,8 +5087,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5083,118 +5200,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3478000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3764000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>785000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4150000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4103000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4027000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1072000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4243000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4171000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4069000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3970000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4280000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4247000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4269000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4183000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3911000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4025000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4144000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4193000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4478000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4499000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5666000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6816000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7505000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7906000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7915000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7901000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6263000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>6052000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6047000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5923000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5183000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>4971000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>5277000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>4882000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>4734000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5303,118 +5426,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>48769000</v>
+      </c>
+      <c r="E54" s="3">
         <v>49002000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>48935000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>49775000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>49373000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>47856000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>47957000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>45813000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>44826000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>43855000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>43135000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>44093000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>42827000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>41967000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>41511000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>41038000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>40908000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>42036000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>42434000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>44066000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>44667000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>48594000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>56312000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>57990000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>70591000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>70321000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>70507000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>70046000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>70156000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>71478000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>71987000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>73569000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>74862000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>76175000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>77956000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>80594000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5453,8 +5582,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5493,668 +5623,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7793000</v>
+      </c>
+      <c r="E57" s="3">
         <v>8121000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4230000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8346000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8082000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8040000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4613000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7922000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7638000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7497000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9121000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9034000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8528000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8638000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8382000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7615000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7635000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7956000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8442000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9201000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9824000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10168000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10663000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10364000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9851000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9702000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10223000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9419000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9367000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9598000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10036000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9676000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9413000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9380000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>9939000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>9378000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2807000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3475000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1237000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1059000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1050000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1441000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1123000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1998000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1993000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2140000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1632000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>899000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>901000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>923000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>909000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1025000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>36000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>749000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>850000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1292000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>603000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1233000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>524000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>340000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>98000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>99000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1407000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3215000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3736000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>4586000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3324000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1289000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2224000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2449000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3153000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3739000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3435000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3440000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5869000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3294000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3277000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3398000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6034000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2608000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2532000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2615000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1265000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1201000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1154000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1135000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1068000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1095000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1113000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1168000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1199000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1158000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1238000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1861000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1911000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1779000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1824000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1896000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1856000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1966000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1963000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2011000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1922000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2049000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1890000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1947000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1967000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1855000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14035000</v>
+      </c>
+      <c r="E60" s="3">
         <v>15036000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12811000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12699000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12409000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12879000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13395000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12528000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12163000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12252000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12018000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11134000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10583000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10696000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10359000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9735000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8784000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9873000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10491000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11651000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11665000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>13262000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>13098000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>12483000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>11773000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>11697000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>13486000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>14600000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>15066000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>16195000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>15282000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>13014000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>13527000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>13776000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>15059000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>14972000</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10895000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10663000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11762000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11928000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12314000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10838000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10909000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11388000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11497000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10981000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10594000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12452000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12946000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13163000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13286000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14370000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>15687000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>15834000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>16036000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>16471000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>16763000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>15409000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14770000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>16333000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>16978000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>16449000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>14644000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>14159000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>13865000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>13526000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>14875000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>15871000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>16600000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>16538000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>16463000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>17538000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1774000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2011000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1433000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2073000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2060000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1924000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1979000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1867000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1882000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1880000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2534000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2996000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2673000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2469000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2580000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3268000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3378000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3357000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3418000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3575000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3783000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3940000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4268000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4847000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>5567000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5651000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5791000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4339000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4328000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4431000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4569000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4674000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4783000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4807000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>4905000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>5510000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6263,8 +6412,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6373,8 +6525,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6483,118 +6638,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27218000</v>
+      </c>
+      <c r="E66" s="3">
         <v>28254000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26585000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>27047000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>27093000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25933000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>26598000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26106000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25892000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25475000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>25450000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26894000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>26502000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>26620000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>26507000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>27676000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>28146000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>29493000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>30363000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>32125000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>32627000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>33033000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>32552000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>34077000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>34739000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>34218000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>34345000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>33513000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>33672000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>34554000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>35145000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>33996000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>35342000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>35569000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>36878000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>38360000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6633,8 +6794,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6743,8 +6905,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6853,8 +7018,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6963,8 +7131,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7073,118 +7244,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17433000</v>
+      </c>
+      <c r="E72" s="3">
         <v>16804000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>16395000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15687000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14890000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>14172000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>13497000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>12742000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11974000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11296000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>10719000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9904000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9244000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8532000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8199000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7775000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7399000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7142000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7018000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6818000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7073000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>10681000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18751000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>19111000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>31186000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>31386000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>31658000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>31712000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>31760000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>32022000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>32190000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>35136000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>35284000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>36052000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>36470000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>37370000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7293,8 +7470,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7403,8 +7583,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7513,118 +7696,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20302000</v>
+      </c>
+      <c r="E76" s="3">
         <v>19515000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21130000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21511000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21071000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20736000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20189000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19386000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18608000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18068000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17685000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17199000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16325000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15347000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15004000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13362000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12762000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12543000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12071000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11941000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12040000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15561000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>23760000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>23913000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>35852000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>36103000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>36162000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>36533000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>36484000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>36924000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>36842000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>39573000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>39520000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>40606000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>41078000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>42234000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7733,233 +7922,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1014000</v>
+      </c>
+      <c r="E81" s="3">
         <v>797000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1095000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1186000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1112000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1068000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1112000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1123000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1033000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>934000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1064000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>907000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>959000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>510000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>601000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>550000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>431000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>299000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>374000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-82000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3434000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7376000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>333000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-11383000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>492000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>421000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>539000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>644000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>430000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>525000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>545000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-74000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>279000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-205000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7998,118 +8196,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>549000</v>
+      </c>
+      <c r="E83" s="3">
         <v>519000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>56000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>501000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>484000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>487000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>71000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>457000</v>
       </c>
       <c r="K83" s="3">
         <v>457000</v>
       </c>
       <c r="L83" s="3">
+        <v>457000</v>
+      </c>
+      <c r="M83" s="3">
         <v>458000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>549000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>533000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>532000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>533000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>532000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>530000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>526000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>532000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>583000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>587000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>604000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>792000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>848000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>900000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>938000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>903000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>919000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>887000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>876000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>874000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>906000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>956000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>986000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>989000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1016000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>998000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8218,8 +8420,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8328,8 +8533,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8438,8 +8646,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8548,8 +8759,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8658,118 +8872,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1142000</v>
+      </c>
+      <c r="E89" s="3">
         <v>660000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2390000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2449000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1436000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>327000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3022000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1677000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1608000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>330000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1614000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1567000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>408000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>131000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1932000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1070000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1220000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>429000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>878000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>479000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>803000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>784000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2252000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1745000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1108000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>326000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2331000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1827000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>987000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>568000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2251000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1898000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>858000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>656000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2013000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1406000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8808,118 +9028,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-488000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-506000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-702000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-594000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-598000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-520000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-710000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-602000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-591000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-543000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-572000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-382000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-360000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-304000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-447000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-273000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-243000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-178000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-258000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-251000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-407000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-494000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-413000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-404000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-413000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-621000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-565000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-520000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-454000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-625000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-598000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-503000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-381000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-654000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-403000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9028,8 +9252,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9138,118 +9365,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-432000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-477000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1024000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1493000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-151000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-520000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-733000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-983000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-547000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-272000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1083000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>82000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-115000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-526000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-619000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>15000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>211000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>246000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-740000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-547000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1312000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-203000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-934000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-644000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-230000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-315000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-895000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-112000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>282000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>221000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>473000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-55000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-32000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9288,28 +9521,29 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>387000</v>
+      </c>
+      <c r="E96" s="3">
         <v>386000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>389000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>393000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>394000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>357000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>356000</v>
       </c>
       <c r="J96" s="3">
         <v>356000</v>
@@ -9318,19 +9552,19 @@
         <v>356000</v>
       </c>
       <c r="L96" s="3">
+        <v>356000</v>
+      </c>
+      <c r="M96" s="3">
         <v>249000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-248000</v>
       </c>
       <c r="N96" s="3">
         <v>-248000</v>
       </c>
       <c r="O96" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-177000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-175000</v>
       </c>
       <c r="Q96" s="3">
         <v>-175000</v>
@@ -9342,7 +9576,7 @@
         <v>-175000</v>
       </c>
       <c r="T96" s="3">
-        <v>-174000</v>
+        <v>-175000</v>
       </c>
       <c r="U96" s="3">
         <v>-174000</v>
@@ -9351,10 +9585,10 @@
         <v>-174000</v>
       </c>
       <c r="W96" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-694000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-692000</v>
       </c>
       <c r="Y96" s="3">
         <v>-692000</v>
@@ -9363,34 +9597,34 @@
         <v>-692000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-692000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-692000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-693000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-692000</v>
       </c>
       <c r="AG96" s="3">
         <v>-692000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-697000</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-696000</v>
       </c>
       <c r="AK96" s="3">
         <v>-696000</v>
@@ -9398,8 +9632,11 @@
       <c r="AL96" s="3">
         <v>-696000</v>
       </c>
+      <c r="AM96" s="3">
+        <v>-696000</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9508,8 +9745,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9618,8 +9858,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9728,334 +9971,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1111000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-878000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1431000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1295000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>221000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-267000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2009000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-382000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-183000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>62000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1844000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-180000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-188000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-170000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1220000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-322000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1070000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-212000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1504000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>21000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-167000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>777000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2097000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1090000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-234000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-297000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2069000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-900000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1264000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-787000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>278000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2342000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1332000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1637000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2389000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1116000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-21000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-81000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-13000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-23000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-17000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-23000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-17000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-9000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>6000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>5000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>6000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>10000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>9000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-104000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>300000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-608000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>458000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>133000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>165000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-112000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>412000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>558000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>429000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-154000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-525000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>287000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>293000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-157000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>188000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>130000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>171000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>424000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-375000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-243000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>87000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>238000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-46000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-283000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>236000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-203000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-60000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>32000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-404000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>66000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>109000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-213000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1027000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-512000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>494000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
@@ -656,519 +656,531 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9745000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8928000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8546000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8490000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9284000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9159000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9139000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8707000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8990000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8310000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8099000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7736000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7878000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7477000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6773000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5962000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6225000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5847000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5634000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5223000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5532000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5258000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5356000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7455000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8228000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8541000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8269000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7879000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8179000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8504000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8303000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>7829000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8179000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>7905000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7462000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6894000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>7107000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>7019000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7916000</v>
+      </c>
+      <c r="E9" s="3">
         <v>7304000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6934000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6884000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7323000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7223000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7247000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6993000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7093000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6592000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6502000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6285000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6307000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6042000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5568000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5013000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5136000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4862000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4768000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4504000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4828000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4624000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4925000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6614000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7136000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>7382000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>7236000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>6956000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7193000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>7305000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>7184000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>6834000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>7169000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>6787000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>6469000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>6082000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>6113000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>6114000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1829000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1624000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1612000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1606000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1961000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1936000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1892000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1714000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1897000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1718000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1597000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1451000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1571000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1435000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1205000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>949000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1089000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>985000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>866000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>719000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>704000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>634000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>431000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>841000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1092000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1159000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1033000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>923000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>986000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1199000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1119000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>995000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1010000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1118000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>993000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>812000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>994000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>905000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1209,124 +1221,128 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>187000</v>
+      </c>
+      <c r="E12" s="3">
         <v>170000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>180000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>172000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>192000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>187000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>188000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>182000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>187000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>186000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>163000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>174000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>178000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>160000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>154000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>141000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>145000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>140000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>134000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>135000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>128000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>137000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>142000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>173000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>190000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>176000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>179000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>173000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>178000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>177000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>175000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>172000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>192000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>189000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>196000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>211000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>262000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1441,62 +1457,65 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>562000</v>
+      </c>
+      <c r="E14" s="3">
         <v>318000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>21000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>206000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>262000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>112000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>142000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>25000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>146000</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" s="3">
         <v>-36000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-83000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-216000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-26000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-28000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
@@ -1504,100 +1523,103 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>-42000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>350000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>3724000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>8523000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>209000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>12692000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-43000</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>184000</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>2796000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>49000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>591000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>82000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>676000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>237000</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E15" s="3">
         <v>638000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>633000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>640000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>640000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>631000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>600000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>56000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>579000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>561000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>563000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1673,8 +1695,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1712,240 +1737,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>8187000</v>
+      </c>
+      <c r="E17" s="3">
         <v>7546000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7201000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7152000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7595000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7500000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7529000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7296000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7376000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6859000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6761000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6550000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6501000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6296000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5592000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5225000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5361000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5082000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4972000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4720000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4986000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5196000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8872000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>15437000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7664000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>20370000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7529000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7241000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7442000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7587000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7657000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7117000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>10266000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>7140000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>7366000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>6473000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>7149000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>6696000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1558000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1382000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1345000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1338000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1689000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1659000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1610000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1411000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1614000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1451000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1338000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1186000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1377000</v>
-      </c>
-      <c r="P18" s="3">
-        <v>1181000</v>
       </c>
       <c r="Q18" s="3">
         <v>1181000</v>
       </c>
       <c r="R18" s="3">
+        <v>1181000</v>
+      </c>
+      <c r="S18" s="3">
         <v>737000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>864000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>765000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>662000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>503000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>546000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>62000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3516000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-7982000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>564000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-11829000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>740000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>638000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>737000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>917000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>646000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>712000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-2087000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>765000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>96000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>421000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-42000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>323000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1986,8 +2018,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1995,579 +2028,594 @@
         <v>-41000</v>
       </c>
       <c r="E20" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-72000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-42000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-46000</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3">
         <v>-46000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-54000</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O20" s="3">
         <v>-39000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>91000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>75000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>95000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>24000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>29000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>56000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>16000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>19000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>69000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>22000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-59000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-29000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>30000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>20000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>31000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>34000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>16000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>41000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>48000</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>28000</v>
       </c>
       <c r="AI20" s="3">
         <v>28000</v>
       </c>
       <c r="AJ20" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AK20" s="3">
         <v>73000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>92000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>70000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-73000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1797000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2061000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2050000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2020000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1749000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2299000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2241000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2057000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1724000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2030000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1899000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1788000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2017000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1789000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1808000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1294000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1425000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1351000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1204000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1054000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1198000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>671000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2971000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-7219000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1442000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-10909000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1709000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1575000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1672000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1845000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1570000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1614000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-1153000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1794000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1174000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1480000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>901000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1352000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>142000</v>
+        <v>126000</v>
       </c>
       <c r="E22" s="3">
         <v>142000</v>
       </c>
       <c r="F22" s="3">
+        <v>142000</v>
+      </c>
+      <c r="G22" s="3">
         <v>147000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>131000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>136000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>132000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>113000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>130000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>129000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>127000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>117000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>121000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>122000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>124000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>123000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>137000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>130000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>136000</v>
       </c>
       <c r="V22" s="3">
         <v>136000</v>
       </c>
       <c r="W22" s="3">
+        <v>136000</v>
+      </c>
+      <c r="X22" s="3">
         <v>144000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>138000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>52000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>78000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>142000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>162000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>178000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>163000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>105000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>171000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>147000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>97000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>151000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>161000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>171000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>157000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>99000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>943000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1000000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1285000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1063000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1387000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1507000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1421000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1357000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1433000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1395000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1293000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1161000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1347000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1134000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1152000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>638000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>756000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>691000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>542000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>386000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>471000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-54000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3627000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-8089000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>452000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-11971000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>593000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>509000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>648000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>787000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>547000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>643000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-2210000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>677000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>17000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>334000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-214000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>200000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E24" s="3">
         <v>226000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>237000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>234000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>269000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>289000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>276000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>259000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>285000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>259000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>246000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>217000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>265000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>215000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>182000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>118000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>145000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>129000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>99000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>74000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>89000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>19000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-199000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-721000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>109000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-598000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>99000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>79000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>99000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>129000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>106000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>113000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-15000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>121000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>98000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>50000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-19000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2682,240 +2730,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>800000</v>
+      </c>
+      <c r="E26" s="3">
         <v>774000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1048000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>829000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1118000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1218000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1145000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1098000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1148000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1136000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1047000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>944000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1082000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>919000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>970000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>520000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>611000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>562000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>443000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>312000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>382000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-73000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3428000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-7368000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>343000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-11373000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>494000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>430000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>549000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>658000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>441000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>530000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-2195000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>556000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-81000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>284000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-195000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>190000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>824000</v>
+      </c>
+      <c r="E27" s="3">
         <v>739000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1014000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>797000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1095000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1186000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1112000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1068000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1112000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1123000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1033000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>934000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1064000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>907000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>959000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>510000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>601000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>550000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>431000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>299000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>374000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-82000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3434000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7376000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>333000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-11383000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>492000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>421000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>539000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>644000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>430000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>525000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-2178000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>545000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-74000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>279000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-205000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3030,8 +3087,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3110,8 +3170,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>24</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>24</v>
@@ -3128,11 +3188,11 @@
       <c r="AH29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-76000</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>24</v>
@@ -3140,14 +3200,17 @@
       <c r="AL29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AM29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN29" s="3" t="s">
+      <c r="AM29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3262,8 +3325,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3378,8 +3444,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3387,231 +3456,237 @@
         <v>41000</v>
       </c>
       <c r="E32" s="3">
+        <v>41000</v>
+      </c>
+      <c r="F32" s="3">
         <v>72000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>42000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>46000</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="3">
         <v>46000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>54000</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O32" s="3">
         <v>39000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-91000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-75000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-95000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-24000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-29000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-56000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-16000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-19000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-69000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-22000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>59000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>29000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-30000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-48000</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-28000</v>
       </c>
       <c r="AI32" s="3">
         <v>-28000</v>
       </c>
       <c r="AJ32" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="AK32" s="3">
         <v>-73000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-92000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-70000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>73000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-31000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>824000</v>
+      </c>
+      <c r="E33" s="3">
         <v>739000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1014000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>797000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1095000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1186000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1112000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1068000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1112000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1123000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1033000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>934000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1064000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>907000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>959000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>510000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>601000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>550000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>431000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>299000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>374000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-82000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3434000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7376000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>333000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-11383000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>492000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>421000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>539000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>644000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>430000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>525000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>545000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-74000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>279000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-205000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3726,245 +3801,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>824000</v>
+      </c>
+      <c r="E35" s="3">
         <v>739000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1014000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>797000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1095000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1186000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1112000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1068000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1112000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1123000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1033000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>934000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1064000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>907000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>959000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>510000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>601000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>550000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>431000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>299000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>374000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-82000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3434000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7376000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>333000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-11383000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>492000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>421000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>539000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>644000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>430000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>525000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>545000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-74000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>279000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-205000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4005,8 +4089,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4047,1052 +4132,1080 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3036000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3014000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3236000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2936000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3544000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3086000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2953000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2788000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2900000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2488000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1930000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1501000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1655000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2180000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1893000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1600000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1757000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1569000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1439000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1268000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>844000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1219000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1462000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1375000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1137000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1183000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1466000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1230000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1433000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1493000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1461000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1865000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1799000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1690000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1903000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1902000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2929000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3441000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1269000</v>
+      </c>
+      <c r="E42" s="3">
         <v>571000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>511000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>999000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1162000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1387000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1050000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>703000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1089000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1247000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1264000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1003000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1239000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1429000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>923000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1049000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1382000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1373000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1243000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1642000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2162000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2618000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2127000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1969000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1030000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1109000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>882000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>925000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1344000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1361000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1588000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2300000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>3290000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>3262000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>4315000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>5451000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>6328000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>7315000</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8689000</v>
+      </c>
+      <c r="E43" s="3">
         <v>9101000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8586000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8604000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8011000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8260000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8605000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8222000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7812000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8049000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7675000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7578000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7032000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6650000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6247000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5713000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5315000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5349000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5347000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5269000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5247000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5552000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5808000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7486000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7747000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8332000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8471000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8171000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7881000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>8409000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8606000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>8472000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>8084000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>9436000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>8925000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>8636000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>9387000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>9565000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5032000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5321000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4740000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4650000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4375000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4573000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4504000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4549000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4387000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4305000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4360000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4286000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3999000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4143000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3968000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3719000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3272000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3296000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3267000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3303000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3354000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3542000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3601000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4148000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4130000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4341000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4389000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4224000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4010000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4108000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4120000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4174000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4046000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4308000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4338000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>4288000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>4225000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>4572000</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1487000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1461000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1380000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1406000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1478000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1495000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1405000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1438000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1530000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>949000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>925000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1032000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1078000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1209000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1285000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1172000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>928000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>800000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>781000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1325000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1312000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1284000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1381000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1288000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1486000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1186000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1125000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1223000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1063000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1112000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1125000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1244000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1278000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1218000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1792000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1606000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1058000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1532000</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19513000</v>
+      </c>
+      <c r="E46" s="3">
         <v>19468000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18453000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18595000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18570000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18801000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18517000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17700000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17718000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17038000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16154000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15400000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15003000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15611000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14316000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>13253000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12654000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12387000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12077000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12807000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12919000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14215000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14379000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16266000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>15530000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16151000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16333000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>15773000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>15731000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>16483000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>16900000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>18055000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>18497000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>19914000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>21273000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>21883000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>23927000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>26425000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3580000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1843000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1888000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1644000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3718000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1783000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1690000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1623000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3735000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1634000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1612000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1561000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1581000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1762000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1767000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1955000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2044000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2110000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2035000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2090000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2061000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1436000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1484000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1515000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1565000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1335000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1558000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1544000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1538000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1497000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1487000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1483000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1519000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1566000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1720000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1637000</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8773000</v>
+      </c>
+      <c r="E48" s="3">
         <v>7999000</v>
-      </c>
-      <c r="E48" s="3">
-        <v>7399000</v>
       </c>
       <c r="F48" s="3">
         <v>7399000</v>
       </c>
       <c r="G48" s="3">
+        <v>7399000</v>
+      </c>
+      <c r="H48" s="3">
         <v>8061000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7360000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7335000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7253000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7958000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6875000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6804000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6691000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6607000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6407000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6386000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6354000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6429000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6375000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6473000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6620000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6826000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7396000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7729000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8550000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9270000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>9605000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11359000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11533000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>11679000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>11739000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>11504000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>11556000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>11576000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12338000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12358000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>12507000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>12821000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>13004000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>22065000</v>
+      </c>
+      <c r="E49" s="3">
         <v>22096000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17551000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17600000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17801000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17681000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>17728000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>17253000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>17474000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16023000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16085000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16134000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15974000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16033000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16111000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>16136000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>16201000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>16255000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>16298000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>16375000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>16435000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>16541000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>16576000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>16597000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>23131000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>23394000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>33435000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>33556000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>33658000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>34064000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>34213000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>34337000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>34472000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>34653000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>34694000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>34788000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>34845000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>34794000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5207,8 +5320,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5323,124 +5439,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>937000</v>
+      </c>
+      <c r="E52" s="3">
         <v>3687000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3478000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3764000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>785000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4150000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4103000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4027000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1072000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4243000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4171000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4069000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3970000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4280000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4247000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4269000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4183000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3911000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4025000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4144000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4193000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4478000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4499000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5666000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6816000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7505000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7906000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7915000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7901000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6263000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>6052000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>6047000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5923000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>5183000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>4971000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>5277000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>4882000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>4734000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5555,124 +5677,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>54868000</v>
+      </c>
+      <c r="E54" s="3">
         <v>55093000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>48769000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>49002000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>48935000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>49775000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>49373000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>47856000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>47957000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>45813000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>44826000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>43855000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>43135000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>44093000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>42827000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>41967000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>41511000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>41038000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>40908000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>42036000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>42434000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>44066000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>44667000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>48594000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>56312000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>57990000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>70591000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>70321000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>70507000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>70046000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>70156000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>71478000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>71987000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>73569000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>74862000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>76175000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>77956000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>80594000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5713,8 +5841,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5755,704 +5884,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4859000</v>
+      </c>
+      <c r="E57" s="3">
         <v>8657000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7793000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8121000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4230000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8346000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8082000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8040000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4613000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7922000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7638000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7497000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9121000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9034000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8528000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8638000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8382000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7615000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7635000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7956000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8442000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9201000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9824000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10168000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10663000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10364000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9851000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9702000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10223000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9419000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9367000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9598000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>10036000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9676000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>9413000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>9380000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>9939000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>9378000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2566000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1923000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2807000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3475000</v>
       </c>
-      <c r="G58" s="3">
-        <v>1237000</v>
-      </c>
       <c r="H58" s="3">
+        <v>1051000</v>
+      </c>
+      <c r="I58" s="3">
         <v>1059000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1050000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1441000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1123000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1998000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1993000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2140000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1632000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>899000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>901000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>923000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>909000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1025000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>36000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>749000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>850000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1292000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>603000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1233000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>524000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>340000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>98000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>99000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1407000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3215000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3736000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>4586000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3324000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1289000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2224000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>2449000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>3153000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>3739000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5710000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3457000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3435000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3440000</v>
       </c>
-      <c r="G59" s="3">
-        <v>5869000</v>
-      </c>
       <c r="H59" s="3">
+        <v>6055000</v>
+      </c>
+      <c r="I59" s="3">
         <v>3294000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3277000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3398000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6034000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2608000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2532000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2615000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1265000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1201000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1154000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1135000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1068000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1095000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1113000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1168000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1199000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1158000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1238000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1861000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1911000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1779000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1824000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1896000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1856000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1966000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1963000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2011000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1922000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2049000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1890000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1947000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1967000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1855000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14721000</v>
+      </c>
+      <c r="E60" s="3">
         <v>14037000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14035000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15036000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12811000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12699000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12409000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12879000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13395000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12528000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12163000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12252000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12018000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11134000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10583000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10696000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10359000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9735000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>8784000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9873000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10491000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11651000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11665000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>13262000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>13098000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>12483000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>11773000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>11697000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>13486000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>14600000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>15066000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>16195000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>15282000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>13014000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>13527000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>13776000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>15059000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>14972000</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9981000</v>
+      </c>
+      <c r="E61" s="3">
         <v>10854000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10895000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10663000</v>
       </c>
-      <c r="G61" s="3">
-        <v>11762000</v>
-      </c>
       <c r="H61" s="3">
+        <v>11206000</v>
+      </c>
+      <c r="I61" s="3">
         <v>11928000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12314000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10838000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10909000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11388000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11497000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10981000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10594000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12452000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12946000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13163000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13286000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14370000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>15687000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>15834000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>16036000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>16471000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>16763000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>15409000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>14770000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>16333000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>16978000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>16449000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>14644000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>14159000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>13865000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>13526000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>14875000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>15871000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>16600000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>16538000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>16463000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>17538000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1752000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1951000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1774000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2011000</v>
       </c>
-      <c r="G62" s="3">
-        <v>1433000</v>
-      </c>
       <c r="H62" s="3">
+        <v>1989000</v>
+      </c>
+      <c r="I62" s="3">
         <v>2073000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2060000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1924000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1979000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1867000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1882000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1880000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2534000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2996000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2673000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2469000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2580000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3268000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3378000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3357000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3418000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3575000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3783000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3940000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4268000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4847000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5567000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5651000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5791000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4339000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4328000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4431000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4569000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4674000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>4783000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>4807000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>4905000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>5510000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6567,8 +6715,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6683,8 +6834,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6799,124 +6953,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27577000</v>
+      </c>
+      <c r="E66" s="3">
         <v>28171000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>27218000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>28254000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>26585000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>27047000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>27093000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25933000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>26598000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>26106000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>25892000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25475000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>25450000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>26894000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>26502000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>26620000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>26507000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>27676000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>28146000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>29493000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>30363000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>32125000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>32627000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>33033000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>32552000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>34077000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>34739000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>34218000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>34345000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>33513000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>33672000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>34554000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>35145000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>33996000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>35342000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>35569000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>36878000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>38360000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6957,8 +7117,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7073,8 +7234,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7189,8 +7353,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7305,8 +7472,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7421,124 +7591,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18067000</v>
+      </c>
+      <c r="E72" s="3">
         <v>17746000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17433000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16804000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16395000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15687000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>14890000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14172000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13497000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12742000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11974000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11296000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>10719000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9904000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9244000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8532000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8199000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7775000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7399000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7142000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7018000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6818000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7073000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>10681000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18751000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>19111000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>31186000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>31386000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>31658000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>31712000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>31760000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>32022000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>32190000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>35136000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>35284000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>36052000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>36470000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>37370000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7653,8 +7829,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7769,8 +7948,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7885,124 +8067,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26109000</v>
+      </c>
+      <c r="E76" s="3">
         <v>25635000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20302000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>19515000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21130000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21511000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21071000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20736000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20189000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19386000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18608000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18068000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17685000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17199000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16325000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15347000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15004000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13362000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12762000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12543000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12071000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11941000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12040000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>15561000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>23760000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>23913000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>35852000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>36103000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>36162000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>36533000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>36484000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>36924000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>36842000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>39573000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>39520000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>40606000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>41078000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>42234000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8117,245 +8305,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>824000</v>
+      </c>
+      <c r="E81" s="3">
         <v>739000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1014000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>797000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1095000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1186000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1112000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1068000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1112000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1123000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1033000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>934000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1064000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>907000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>959000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>510000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>601000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>550000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>431000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>299000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>374000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-82000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3434000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7376000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>333000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-11383000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>492000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>421000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>539000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>644000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>430000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>525000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>545000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-74000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>279000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-205000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8396,124 +8593,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E83" s="3">
         <v>553000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>549000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>519000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>56000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>501000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>484000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>487000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>71000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>457000</v>
       </c>
       <c r="M83" s="3">
         <v>457000</v>
       </c>
       <c r="N83" s="3">
+        <v>457000</v>
+      </c>
+      <c r="O83" s="3">
         <v>458000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>549000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>533000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>532000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>533000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>532000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>530000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>526000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>532000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>583000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>587000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>604000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>792000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>848000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>900000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>938000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>903000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>919000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>887000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>876000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>874000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>906000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>956000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>986000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>989000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>1016000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>998000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8628,8 +8829,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8744,8 +8948,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8860,8 +9067,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8976,8 +9186,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9092,124 +9305,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3005000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1682000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1142000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>660000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2390000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2449000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1436000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>327000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3022000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1677000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1608000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>330000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1614000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1567000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>408000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>131000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1932000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1070000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1220000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>429000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>878000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>479000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>803000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>784000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2252000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1745000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1108000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>326000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2331000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1827000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>987000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>568000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2251000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1898000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>858000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>656000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>2013000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1406000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9250,124 +9469,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-632000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-496000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-488000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-506000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-702000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-594000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-598000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-520000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-710000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-602000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-591000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-543000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-572000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-382000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-360000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-304000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-447000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-273000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-243000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-178000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-258000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-251000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-407000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-494000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-413000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-404000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-413000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-621000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-565000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-520000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-454000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-625000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-598000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-503000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-381000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-654000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-403000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9482,8 +9705,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9598,124 +9824,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1270000</v>
+      </c>
+      <c r="E94" s="3">
         <v>44000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>246000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-432000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-477000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1024000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1493000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-151000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-520000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-733000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-983000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-547000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-272000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1083000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>82000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-115000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-526000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-619000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>15000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>211000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>246000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-740000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-547000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1312000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-203000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-934000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-644000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-230000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-315000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-895000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-112000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>282000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>221000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>473000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-55000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-32000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9756,34 +9988,35 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>426000</v>
+      </c>
+      <c r="E96" s="3">
         <v>403000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>387000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>386000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>389000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>393000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>394000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>357000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>356000</v>
       </c>
       <c r="L96" s="3">
         <v>356000</v>
@@ -9792,19 +10025,19 @@
         <v>356000</v>
       </c>
       <c r="N96" s="3">
+        <v>356000</v>
+      </c>
+      <c r="O96" s="3">
         <v>249000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-248000</v>
       </c>
       <c r="P96" s="3">
         <v>-248000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-177000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-175000</v>
       </c>
       <c r="S96" s="3">
         <v>-175000</v>
@@ -9816,7 +10049,7 @@
         <v>-175000</v>
       </c>
       <c r="V96" s="3">
-        <v>-174000</v>
+        <v>-175000</v>
       </c>
       <c r="W96" s="3">
         <v>-174000</v>
@@ -9825,10 +10058,10 @@
         <v>-174000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-694000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-692000</v>
       </c>
       <c r="AA96" s="3">
         <v>-692000</v>
@@ -9837,34 +10070,34 @@
         <v>-692000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-692000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-692000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-693000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-692000</v>
       </c>
       <c r="AI96" s="3">
         <v>-692000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-697000</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>-696000</v>
       </c>
       <c r="AM96" s="3">
         <v>-696000</v>
@@ -9872,8 +10105,11 @@
       <c r="AN96" s="3">
         <v>-696000</v>
       </c>
+      <c r="AO96" s="3">
+        <v>-696000</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9988,8 +10224,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10104,8 +10343,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10220,352 +10462,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1721000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1932000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1111000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-878000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1431000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1295000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>221000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-267000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2009000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-382000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-183000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>62000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1844000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-180000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-188000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-170000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1220000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-322000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1070000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-212000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1504000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>21000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-167000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>777000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2097000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1090000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-234000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-297000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2069000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-900000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1264000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-787000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>278000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2342000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1332000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1637000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2389000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1116000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E101" s="3">
         <v>3000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-21000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-81000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-13000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-23000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-17000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-23000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-9000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>6000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>5000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>6000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>3000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>10000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>2000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>9000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-104000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-222000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>300000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-608000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>458000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>133000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>165000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-112000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>412000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>558000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>429000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-154000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-525000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>287000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>293000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-157000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>188000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>130000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>171000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>424000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-375000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-243000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>87000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>238000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-46000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-283000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>236000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-203000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-60000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>32000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-404000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>66000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>109000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-213000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-1027000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-512000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>494000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SLB_QTR_FIN.xlsx
@@ -656,531 +656,544 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8721000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9745000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8928000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8546000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8490000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9284000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9159000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9139000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8707000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8990000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8310000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8099000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7736000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7878000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7477000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6773000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5962000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6225000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5847000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5634000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5223000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5532000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5258000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5356000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7455000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8228000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8541000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8269000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>7879000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8179000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8504000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>8303000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>7829000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>8179000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>7905000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>7462000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>6894000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>7107000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>7019000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7390000</v>
+      </c>
+      <c r="E9" s="3">
         <v>7916000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7304000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6934000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6884000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7323000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>7223000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7247000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6993000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7093000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6592000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6502000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6285000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6307000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6042000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5568000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5013000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5136000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4862000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4768000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4504000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4828000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4624000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4925000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6614000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>7136000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>7382000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>7236000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>6956000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>7193000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>7305000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>7184000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6834000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>7169000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>6787000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>6469000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>6082000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>6113000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>6114000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1331000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1829000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1624000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1612000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1606000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1961000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1936000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1892000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1714000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1897000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1718000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1597000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1451000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1571000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1435000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1205000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>949000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1089000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>985000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>866000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>719000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>704000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>634000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>431000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>841000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1092000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1159000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1033000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>923000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>986000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1199000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1119000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>995000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1010000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1118000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>993000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>812000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>994000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>905000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1222,127 +1235,131 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>164000</v>
+      </c>
+      <c r="E12" s="3">
         <v>187000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>170000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>180000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>172000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>192000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>187000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>188000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>182000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>187000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>186000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>163000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>174000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>178000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>160000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>154000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>141000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>145000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>140000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>134000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>135000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>128000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>137000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>142000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>173000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>190000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>176000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>179000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>173000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>178000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>177000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>175000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>172000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>192000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>189000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>196000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>211000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>262000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>253000</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1460,65 +1477,68 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E14" s="3">
         <v>562000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>318000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>21000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>206000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>262000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>112000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>142000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>25000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>146000</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P14" s="3">
         <v>-36000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-83000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-216000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-26000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-28000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
@@ -1526,103 +1546,106 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-42000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>350000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>3724000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>8523000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>209000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>12692000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-43000</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>184000</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>2796000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>49000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>591000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>82000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>676000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>237000</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>685000</v>
+      </c>
+      <c r="E15" s="3">
         <v>198000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>638000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>633000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>640000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>14000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>640000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>631000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>600000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>56000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>579000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>561000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>563000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1698,8 +1721,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1738,246 +1764,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7651000</v>
+      </c>
+      <c r="E17" s="3">
         <v>8187000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7546000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7201000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7152000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7595000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7500000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7529000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7296000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7376000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6859000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6761000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6550000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6501000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6296000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5592000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5225000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5361000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5082000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4972000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4720000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4986000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5196000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8872000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>15437000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7664000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>20370000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7529000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7241000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7442000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7587000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7657000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>7117000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>10266000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>7140000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>7366000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>6473000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>7149000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>6696000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1070000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1558000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1382000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1345000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1338000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1689000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1659000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1610000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1411000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1614000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1451000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1338000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1186000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1377000</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>1181000</v>
       </c>
       <c r="R18" s="3">
         <v>1181000</v>
       </c>
       <c r="S18" s="3">
+        <v>1181000</v>
+      </c>
+      <c r="T18" s="3">
         <v>737000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>864000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>765000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>662000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>503000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>546000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>62000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3516000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-7982000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>564000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-11829000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>740000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>638000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>737000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>917000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>646000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>712000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-2087000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>765000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>96000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>421000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-42000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>323000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2019,603 +2052,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-41000</v>
+        <v>-18000</v>
       </c>
       <c r="E20" s="3">
         <v>-41000</v>
       </c>
       <c r="F20" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-72000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-42000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-46000</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3">
         <v>-46000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-54000</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P20" s="3">
         <v>-39000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>91000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>75000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>95000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>24000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>29000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>56000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>16000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>19000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>69000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>22000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-59000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-29000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>30000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>20000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>31000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>34000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>16000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>41000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>48000</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>28000</v>
       </c>
       <c r="AJ20" s="3">
         <v>28000</v>
       </c>
       <c r="AK20" s="3">
+        <v>28000</v>
+      </c>
+      <c r="AL20" s="3">
         <v>73000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>92000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>70000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-73000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1773000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1797000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2061000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2050000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2020000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1749000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2299000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2241000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2057000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1724000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2030000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1899000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1788000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2017000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1789000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1808000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1294000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1425000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1351000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1204000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1054000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1198000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>671000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2971000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-7219000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1442000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-10909000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1709000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1575000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1672000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1845000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1570000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1614000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-1153000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1794000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1174000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1480000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>901000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1352000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E22" s="3">
         <v>126000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>142000</v>
       </c>
       <c r="F22" s="3">
         <v>142000</v>
       </c>
       <c r="G22" s="3">
+        <v>142000</v>
+      </c>
+      <c r="H22" s="3">
         <v>147000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>131000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>136000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>132000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>113000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>130000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>129000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>127000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>117000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>121000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>122000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>124000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>123000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>137000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>130000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>136000</v>
       </c>
       <c r="W22" s="3">
         <v>136000</v>
       </c>
       <c r="X22" s="3">
+        <v>136000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>144000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>138000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>52000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>78000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>142000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>162000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>178000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>163000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>105000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>171000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>147000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>97000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>151000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>161000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>171000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>157000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>99000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>956000</v>
+      </c>
+      <c r="E23" s="3">
         <v>943000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1000000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1285000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1063000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1387000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1507000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1421000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1357000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1433000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1395000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1293000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1161000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1347000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1134000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1152000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>638000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>756000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>691000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>542000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>386000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>471000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-54000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3627000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-8089000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>452000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-11971000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>593000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>509000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>648000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>787000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>547000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>643000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-2210000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>677000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>17000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>334000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-214000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>200000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>195000</v>
+      </c>
+      <c r="E24" s="3">
         <v>143000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>226000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>237000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>234000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>269000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>289000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>276000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>259000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>285000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>259000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>246000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>217000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>265000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>215000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>182000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>118000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>145000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>129000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>99000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>74000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>89000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>19000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-199000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-721000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>109000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-598000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>99000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>79000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>99000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>129000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>106000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>113000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-15000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>121000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>98000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>50000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-19000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2733,246 +2782,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>761000</v>
+      </c>
+      <c r="E26" s="3">
         <v>800000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>774000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1048000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>829000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1118000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1218000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1145000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1098000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1148000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1136000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1047000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>944000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1082000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>919000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>970000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>520000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>611000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>562000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>443000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>312000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>382000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-73000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3428000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-7368000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>343000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-11373000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>494000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>430000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>549000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>658000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>441000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>530000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-2195000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>556000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-81000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>284000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-195000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>190000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>752000</v>
+      </c>
+      <c r="E27" s="3">
         <v>824000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>739000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1014000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>797000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1095000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1186000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1112000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1068000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1112000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1123000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1033000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>934000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1064000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>907000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>959000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>510000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>601000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>550000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>431000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>299000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>374000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-82000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3434000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-7376000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>333000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-11383000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>492000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>421000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>539000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>644000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>430000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>525000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-2178000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>545000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-74000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>279000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-205000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3090,8 +3148,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3173,8 +3234,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>24</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -3191,11 +3252,11 @@
       <c r="AI29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-76000</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>24</v>
@@ -3203,14 +3264,17 @@
       <c r="AM29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AN29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO29" s="3" t="s">
+      <c r="AN29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3328,8 +3392,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3447,246 +3514,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>41000</v>
+        <v>18000</v>
       </c>
       <c r="E32" s="3">
         <v>41000</v>
       </c>
       <c r="F32" s="3">
+        <v>41000</v>
+      </c>
+      <c r="G32" s="3">
         <v>72000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>42000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>46000</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="3">
         <v>46000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>54000</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P32" s="3">
         <v>39000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-91000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-75000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-95000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-24000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-29000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-56000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-16000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-19000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-69000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-22000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>59000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>29000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-30000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-31000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-34000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-48000</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>-28000</v>
       </c>
       <c r="AJ32" s="3">
         <v>-28000</v>
       </c>
       <c r="AK32" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="AL32" s="3">
         <v>-73000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-92000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-70000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>73000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-31000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>752000</v>
+      </c>
+      <c r="E33" s="3">
         <v>824000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>739000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1014000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>797000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1095000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1186000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1112000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1068000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1112000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1123000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1033000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>934000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1064000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>907000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>959000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>510000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>601000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>550000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>431000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>299000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>374000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-82000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3434000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7376000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>333000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-11383000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>492000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>421000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>539000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>644000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>430000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>525000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>545000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-74000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>279000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-205000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3804,251 +3880,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>752000</v>
+      </c>
+      <c r="E35" s="3">
         <v>824000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>739000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1014000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>797000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1095000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1186000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1112000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1068000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1112000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1123000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1033000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>934000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1064000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>907000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>959000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>510000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>601000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>550000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>431000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>299000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>374000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-82000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3434000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7376000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>333000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-11383000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>492000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>421000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>539000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>644000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>430000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>525000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>545000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-74000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>279000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-205000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4090,8 +4175,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4133,1079 +4219,1107 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2819000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3036000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3014000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3236000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2936000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3544000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3086000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2953000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2788000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2900000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2488000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1930000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1501000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1655000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2180000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1893000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1600000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1757000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1569000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1439000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1268000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>844000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1219000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1462000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1375000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1137000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1183000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1466000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1230000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1433000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1493000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1461000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1865000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1799000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1690000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1903000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1902000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2929000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>3441000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>633000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1269000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>571000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>511000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>999000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1162000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1387000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1050000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>703000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1089000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1247000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1264000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1003000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1239000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1429000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>923000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1049000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1382000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1373000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1243000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1642000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2162000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2618000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2127000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1969000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1030000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1109000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>882000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>925000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1344000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1361000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1588000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>2300000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>3290000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>3262000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>4315000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>5451000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>6328000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>7315000</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9037000</v>
+      </c>
+      <c r="E43" s="3">
         <v>8689000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9101000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8586000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8604000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8011000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8260000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8605000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8222000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7812000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8049000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7675000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7578000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7032000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6650000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6247000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5713000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5315000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5349000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5347000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5269000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5247000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5552000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5808000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7486000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7747000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>8332000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>8471000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>8171000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7881000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8409000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>8606000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>8472000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>8084000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>9436000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>8925000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>8636000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>9387000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>9565000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5274000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5032000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5321000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4740000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4650000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4375000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4573000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4504000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4549000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4387000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4305000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4360000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4286000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3999000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4143000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3968000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3719000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3272000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3296000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3267000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3303000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3354000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3542000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3601000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4148000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4130000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4341000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4389000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4224000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4010000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4108000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4120000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4174000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4046000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4308000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>4338000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>4288000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>4225000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>4572000</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1572000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1487000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1461000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1380000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1406000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1478000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1495000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1405000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1438000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1530000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>949000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>925000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1032000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1078000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1209000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1285000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1172000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>928000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>800000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>781000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1325000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1312000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1284000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1381000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1288000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1486000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1186000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1125000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1223000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1063000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1112000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1125000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1244000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1278000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1218000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1792000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1606000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1058000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>1532000</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>19335000</v>
+      </c>
+      <c r="E46" s="3">
         <v>19513000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19468000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18453000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18595000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18570000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18801000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18517000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17700000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17718000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17038000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16154000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15400000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15003000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15611000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14316000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>13253000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12654000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12387000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12077000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12807000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>12919000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14215000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>14379000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16266000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>15530000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16151000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>16333000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>15773000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>15731000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>16483000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>16900000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>18055000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>18497000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>19914000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>21273000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>21883000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>23927000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>26425000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1830000</v>
+      </c>
+      <c r="E47" s="3">
         <v>3580000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1843000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1888000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1644000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3718000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1783000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1690000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1623000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3735000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1634000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1612000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1561000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1581000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1762000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1767000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1955000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2044000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2110000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2035000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2090000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2061000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1436000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1484000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1515000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1565000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1335000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1558000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1544000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1538000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1497000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1487000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1483000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1519000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1566000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1720000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1481000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1637000</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7747000</v>
+      </c>
+      <c r="E48" s="3">
         <v>8773000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7999000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>7399000</v>
       </c>
       <c r="G48" s="3">
         <v>7399000</v>
       </c>
       <c r="H48" s="3">
+        <v>7399000</v>
+      </c>
+      <c r="I48" s="3">
         <v>8061000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7360000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7335000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7253000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7958000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6875000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6804000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6691000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6607000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6407000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6386000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6354000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6429000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6375000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6473000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6620000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6826000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7396000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7729000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8550000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>9270000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9605000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11359000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>11533000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>11679000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>11739000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>11504000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>11556000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>11576000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12338000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>12358000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>12507000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>12821000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>13004000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>21753000</v>
+      </c>
+      <c r="E49" s="3">
         <v>22065000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22096000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17551000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17600000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17801000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>17681000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>17728000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>17253000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>17474000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16023000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16085000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16134000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15974000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16033000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>16111000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>16136000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>16201000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>16255000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>16298000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>16375000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>16435000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>16541000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>16576000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>16597000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>23131000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>23394000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>33435000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>33556000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>33658000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>34064000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>34213000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>34337000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>34472000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>34653000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>34694000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>34788000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>34845000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>34794000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5323,8 +5437,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5442,127 +5559,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3861000</v>
+      </c>
+      <c r="E52" s="3">
         <v>937000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3687000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3478000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3764000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>785000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4150000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4103000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4027000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1072000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4243000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4171000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4069000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3970000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4280000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4247000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4269000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4183000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3911000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4025000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4144000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4193000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4478000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4499000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5666000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6816000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7505000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7906000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7915000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7901000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>6263000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>6052000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>6047000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>5923000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>5183000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>4971000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>5277000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>4882000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>4734000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5680,127 +5803,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>54526000</v>
+      </c>
+      <c r="E54" s="3">
         <v>54868000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>55093000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>48769000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>49002000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>48935000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>49775000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>49373000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>47856000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>47957000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>45813000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>44826000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>43855000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>43135000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>44093000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>42827000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>41967000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>41511000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>41038000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>40908000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>42036000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>42434000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>44066000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>44667000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>48594000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>56312000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>57990000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>70591000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>70321000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>70507000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>70046000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>70156000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>71478000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>71987000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>73569000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>74862000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>76175000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>77956000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>80594000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5842,8 +5971,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5885,722 +6015,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8640000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4859000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8657000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7793000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8121000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4230000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>8346000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8082000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8040000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4613000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7922000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7638000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7497000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9121000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9034000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8528000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8638000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8382000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7615000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7635000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7956000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>8442000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9201000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9824000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10168000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10663000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10364000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9851000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9702000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10223000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9419000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9367000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9598000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>10036000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>9676000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>9413000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>9380000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>9939000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>9378000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1938000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2566000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1923000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2807000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3475000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1051000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1059000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1050000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1441000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1123000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1998000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1993000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2140000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1632000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>899000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>901000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>923000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>909000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1025000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>36000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>749000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>850000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1292000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>603000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1233000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>524000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>340000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>98000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>99000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1407000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3215000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3736000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>4586000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3324000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1289000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>2224000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>2449000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>3153000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>3739000</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3835000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5710000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3457000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3435000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3440000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6055000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3294000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3277000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3398000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6034000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2608000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2532000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2615000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1265000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1201000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1154000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1135000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1068000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1095000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1113000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1168000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1199000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1158000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1238000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1861000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1911000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1779000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1824000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1896000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1856000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1966000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1963000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2011000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1922000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2049000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1890000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1947000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1967000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1855000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14413000</v>
+      </c>
+      <c r="E60" s="3">
         <v>14721000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14037000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14035000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15036000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12811000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12699000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12409000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12879000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13395000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12528000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12163000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12252000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12018000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11134000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10583000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10696000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10359000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9735000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>8784000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9873000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10491000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11651000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>11665000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>13262000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>13098000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>12483000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>11773000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>11697000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>13486000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>14600000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>15066000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>16195000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>15282000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>13014000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>13527000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>13776000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>15059000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>14972000</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9691000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9981000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10854000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10895000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10663000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11206000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11928000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12314000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10838000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10909000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11388000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11497000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10981000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10594000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12452000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12946000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13163000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>13286000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>14370000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>15687000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>15834000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>16036000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>16471000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>16763000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>15409000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>14770000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>16333000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>16978000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>16449000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>14644000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>14159000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>13865000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>13526000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>14875000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>15871000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>16600000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>16538000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>16463000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>17538000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1891000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1752000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1951000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1774000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2011000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1989000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2073000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2060000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1924000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1979000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1867000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1882000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1880000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2534000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2996000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2673000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2469000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2580000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3268000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3378000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3357000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3418000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3575000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3783000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3940000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4268000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4847000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5567000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5651000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5791000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>4339000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4328000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4431000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4569000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>4674000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>4783000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>4807000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>4905000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>5510000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6718,8 +6867,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6837,8 +6989,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6956,127 +7111,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27173000</v>
+      </c>
+      <c r="E66" s="3">
         <v>27577000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>28171000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>27218000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>28254000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>26585000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>27047000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>27093000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25933000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>26598000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26106000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25892000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>25475000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>25450000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>26894000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>26502000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>26620000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>26507000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>27676000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>28146000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>29493000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>30363000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>32125000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>32627000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>33033000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>32552000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>34077000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>34739000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>34218000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>34345000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>33513000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>33672000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>34554000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>35145000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>33996000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>35342000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>35569000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>36878000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>38360000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7118,8 +7279,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7237,8 +7399,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7356,8 +7521,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7475,8 +7643,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7594,127 +7765,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18369000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18067000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17746000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17433000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16804000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16395000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15687000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14890000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14172000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13497000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12742000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11974000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11296000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>10719000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>9904000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9244000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8532000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8199000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7775000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7399000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7142000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7018000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6818000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7073000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>10681000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>18751000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>19111000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>31186000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>31386000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>31658000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>31712000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>31760000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>32022000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>32190000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>35136000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>35284000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>36052000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>36470000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>37370000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7832,8 +8009,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7951,8 +8131,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8070,127 +8253,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26177000</v>
+      </c>
+      <c r="E76" s="3">
         <v>26109000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>25635000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20302000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>19515000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>21130000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>21511000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>21071000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20736000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20189000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19386000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18608000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>18068000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>17685000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17199000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16325000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15347000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15004000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13362000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12762000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12543000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12071000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11941000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12040000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15561000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>23760000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>23913000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>35852000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>36103000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>36162000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>36533000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>36484000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>36924000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>36842000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>39573000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>39520000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>40606000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>41078000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>42234000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8308,251 +8497,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>752000</v>
+      </c>
+      <c r="E81" s="3">
         <v>824000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>739000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1014000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>797000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1095000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1186000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1112000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1068000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1112000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1123000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1033000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>934000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1064000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>907000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>959000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>510000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>601000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>550000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>431000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>299000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>374000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-82000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3434000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7376000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>333000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-11383000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>492000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>421000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>539000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>644000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>430000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>525000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-2254000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>545000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-74000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>279000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-205000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>176000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8594,127 +8792,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>558000</v>
+      </c>
+      <c r="E83" s="3">
         <v>14000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>553000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>549000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>519000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>56000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>501000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>484000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>487000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>71000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>457000</v>
       </c>
       <c r="N83" s="3">
         <v>457000</v>
       </c>
       <c r="O83" s="3">
+        <v>457000</v>
+      </c>
+      <c r="P83" s="3">
         <v>458000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>549000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>533000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>532000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>533000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>532000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>530000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>526000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>532000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>583000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>587000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>604000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>792000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>848000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>900000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>938000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>903000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>919000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>887000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>876000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>874000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>906000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>956000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>986000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>989000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>1016000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>998000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8832,8 +9034,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8951,8 +9156,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9070,8 +9278,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9189,8 +9400,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9308,127 +9522,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>487000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3005000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1682000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1142000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>660000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2390000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2449000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1436000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>327000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3022000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1677000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1608000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>330000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1614000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1567000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>408000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>131000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1932000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1070000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1220000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>429000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>878000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>479000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>803000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>784000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2252000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1745000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1108000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>326000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2331000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1827000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>987000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>568000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2251000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1898000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>858000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>656000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>2013000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1406000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9470,127 +9690,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-446000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-632000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-496000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-488000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-506000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-702000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-594000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-598000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-520000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-710000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-602000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-591000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-543000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-572000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-382000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-360000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-304000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-447000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-273000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-243000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-178000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-258000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-200000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-251000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-407000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-494000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-413000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-404000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-413000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-621000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-565000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-520000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-454000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-625000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-598000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-503000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-381000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-654000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-403000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9708,8 +9932,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9827,127 +10054,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1270000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>44000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>246000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-432000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-477000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1024000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1493000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-151000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-520000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-733000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-983000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-547000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-272000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1083000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>82000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-115000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-526000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-619000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>15000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>211000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>246000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-740000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-547000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1312000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-203000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-934000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-644000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-230000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-315000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-895000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-112000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>282000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2418000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>221000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>473000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-55000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-32000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>186000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9989,8 +10222,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9998,28 +10232,28 @@
         <v>426000</v>
       </c>
       <c r="E96" s="3">
+        <v>426000</v>
+      </c>
+      <c r="F96" s="3">
         <v>403000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>387000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>386000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>389000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>393000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>394000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>357000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>356000</v>
       </c>
       <c r="M96" s="3">
         <v>356000</v>
@@ -10028,19 +10262,19 @@
         <v>356000</v>
       </c>
       <c r="O96" s="3">
+        <v>356000</v>
+      </c>
+      <c r="P96" s="3">
         <v>249000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-248000</v>
       </c>
       <c r="Q96" s="3">
         <v>-248000</v>
       </c>
       <c r="R96" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-177000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-175000</v>
       </c>
       <c r="T96" s="3">
         <v>-175000</v>
@@ -10052,7 +10286,7 @@
         <v>-175000</v>
       </c>
       <c r="W96" s="3">
-        <v>-174000</v>
+        <v>-175000</v>
       </c>
       <c r="X96" s="3">
         <v>-174000</v>
@@ -10061,10 +10295,10 @@
         <v>-174000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-174000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-694000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-692000</v>
       </c>
       <c r="AB96" s="3">
         <v>-692000</v>
@@ -10073,34 +10307,34 @@
         <v>-692000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-692000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-692000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-693000</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-692000</v>
       </c>
       <c r="AJ96" s="3">
         <v>-692000</v>
       </c>
       <c r="AK96" s="3">
+        <v>-692000</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-693000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-697000</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-696000</v>
       </c>
       <c r="AN96" s="3">
         <v>-696000</v>
@@ -10108,8 +10342,11 @@
       <c r="AO96" s="3">
         <v>-696000</v>
       </c>
+      <c r="AP96" s="3">
+        <v>-696000</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10227,8 +10464,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10346,8 +10586,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10465,361 +10708,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-734000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1721000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1932000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1111000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-878000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1431000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1295000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>221000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-267000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2009000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-382000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-183000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>62000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1844000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-180000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-188000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-170000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1220000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-322000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1070000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-212000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1504000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>21000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-167000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>777000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2097000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1090000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-234000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-297000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2069000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-900000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1264000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-787000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>278000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2342000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1332000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1637000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-2389000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1116000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-24000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-21000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-81000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-13000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-23000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-17000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-17000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-9000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>6000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-4000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>5000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>2000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>6000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>10000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>2000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>9000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-104000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-217000</v>
+      </c>
+      <c r="E102" s="3">
         <v>22000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-222000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>300000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-608000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>458000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>133000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>165000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-112000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>412000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>558000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>429000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-154000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-525000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>287000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>293000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-157000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>188000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>130000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>171000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>424000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-375000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-243000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>87000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>238000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-46000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-283000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>236000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-203000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-60000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>32000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-404000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>66000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>109000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-213000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-1027000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-512000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>494000</v>
       </c>
     </row>
